--- a/shacl/RUIM-SHACL-instances.xlsx
+++ b/shacl/RUIM-SHACL-instances.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Préfixes" sheetId="1" state="visible" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="829">
   <si>
     <t>PREFIX</t>
   </si>
@@ -878,7 +878,7 @@
     <t>sh:datatype</t>
   </si>
   <si>
-    <t>med:sousClasseDe</t>
+    <t>sh:class</t>
   </si>
   <si>
     <t>dash:propertyRole</t>
@@ -2242,7 +2242,7 @@
     <t xml:space="preserve">Note : le range est défini comme un sh:or vers les spécialités ou les présentations</t>
   </si>
   <si>
-    <t xml:space="preserve">([med:sousClasseDe med:SpecialitePharmaceutique][med:sousClasseDe med:Presentation])</t>
+    <t xml:space="preserve">([sh:class med:SpecialitePharmaceutique][sh:class med:Presentation])</t>
   </si>
   <si>
     <t>med:typeEvenement</t>
@@ -2389,7 +2389,7 @@
   FILTER NOT EXISTS {
     $this med:presente/med:prescriptibiliteEnDC ?niveauDc .
    # prescriptible en DC + avec nom de marque
-    FILTER( ?niveauDc IN(med:NiveauPrescriptibilite_315 med:NiveauPrescriptibilite_317))
+    FILTER( ?niveauDc IN(med:NiveauPrescriptibilite_315, med:NiveauPrescriptibilite_317))
   }
 }</t>
   </si>
@@ -2406,7 +2406,7 @@
 WHERE {
   $this med:presente/med:prescriptibiliteEnDC ?niveauDc .
    # prescriptible en DC + avec nom de marque
-   FILTER( ?niveauDc IN(med:NiveauPrescriptibilite_315 med:NiveauPrescriptibilite_317))
+   FILTER( ?niveauDc IN(med:NiveauPrescriptibilite_315, med:NiveauPrescriptibilite_317))
   FILTER NOT EXISTS {
     $this med:prescriptibleComme ?dc .
   }
@@ -2590,7 +2590,7 @@
 SELECT $this ?value
 WHERE {
   $this med:prescriptibiliteEnDC ?value .
-  FILTER(?value NOT IN (med:NiveauPrescriptibilite_315 med:NiveauPrescriptibilite_316))
+  FILTER(?value NOT IN (med:NiveauPrescriptibilite_315, med:NiveauPrescriptibilite_316))
   FILTER NOT EXISTS {
     $this med:justificationPrescriptibiliteEnDC ?justification .
   }
@@ -2664,6 +2664,9 @@
   </si>
   <si>
     <t>sh:NodeShape</t>
+  </si>
+  <si>
+    <t>med:sousClasseDe</t>
   </si>
   <si>
     <t>med:turnIntoShClass</t>
@@ -2835,7 +2838,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="10.000000"/>
       <color theme="1"/>
@@ -2907,6 +2910,12 @@
     <font>
       <sz val="10.000000"/>
       <name val="&quot;Arial&quot;"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10.000000"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -3085,7 +3094,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="107">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3256,6 +3265,19 @@
     <xf fontId="7" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf fontId="8" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="12" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="8" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf fontId="7" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3278,7 +3300,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="10" fillId="15" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="12" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="13" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="7" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3291,7 +3316,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="14" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="16" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3303,7 +3328,7 @@
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="14" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="15" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3312,7 +3337,7 @@
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf fontId="14" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="15" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4343,7 +4368,7 @@
         <v>59</v>
       </c>
       <c r="Q10" t="str">
-        <f>IF(NOT(ISBLANK(P10)),CONCATENATE("""^",$B$1,"/",P10,"$"""),"")</f>
+        <f t="shared" ref="Q10:Q52" si="0">IF(NOT(ISBLANK(P10)),CONCATENATE("""^",$B$1,"/",P10,"$"""),"")</f>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/SpecialitePharmaceutique_.*$"</v>
       </c>
       <c r="R10" s="2" t="s">
@@ -4362,7 +4387,7 @@
         <v>63</v>
       </c>
       <c r="D11" s="8">
-        <f t="shared" ref="D11:D52" si="0">ROW(A11)</f>
+        <f t="shared" ref="D11:D52" si="1">ROW(A11)</f>
         <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -4392,7 +4417,7 @@
         <v>65</v>
       </c>
       <c r="Q11" t="str">
-        <f>IF(NOT(ISBLANK(P11)),CONCATENATE("""^",$B$1,"/",P11,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/Presentation_.*$"</v>
       </c>
       <c r="R11" s="2" t="s">
@@ -4410,7 +4435,7 @@
         <v>69</v>
       </c>
       <c r="D12" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -4440,7 +4465,7 @@
         <v>71</v>
       </c>
       <c r="Q12" t="str">
-        <f>IF(NOT(ISBLANK(P12)),CONCATENATE("""^",$B$1,"/",P12,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/UCD_.*$"</v>
       </c>
       <c r="R12" s="2" t="s">
@@ -4458,7 +4483,7 @@
         <v>75</v>
       </c>
       <c r="D13" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -4486,7 +4511,7 @@
         <v>77</v>
       </c>
       <c r="Q13" t="str">
-        <f>IF(NOT(ISBLANK(P13)),CONCATENATE("""^",$B$1,"/",P13,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/GroupeGenerique_.*$"</v>
       </c>
       <c r="R13" s="2" t="s">
@@ -4504,7 +4529,7 @@
         <v>80</v>
       </c>
       <c r="D14" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -4534,7 +4559,7 @@
         <v>83</v>
       </c>
       <c r="Q14" t="str">
-        <f>IF(NOT(ISBLANK(P14)),CONCATENATE("""^",$B$1,"/",P14,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/Element_.*$"</v>
       </c>
       <c r="R14" s="2" t="s">
@@ -4553,7 +4578,7 @@
         <v>87</v>
       </c>
       <c r="D15" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -4583,7 +4608,7 @@
         <v>89</v>
       </c>
       <c r="Q15" t="str">
-        <f>IF(NOT(ISBLANK(P15)),CONCATENATE("""^",$B$1,"/",P15,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/ElementPresentation_.*$"</v>
       </c>
       <c r="R15" s="2" t="s">
@@ -4639,7 +4664,7 @@
         <v>93</v>
       </c>
       <c r="D17" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -4669,7 +4694,7 @@
         <v>95</v>
       </c>
       <c r="Q17" t="str">
-        <f>IF(NOT(ISBLANK(P17)),CONCATENATE("""^",$B$1,"/",P17,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/Dosage_.*$"</v>
       </c>
       <c r="R17" s="2">
@@ -4687,7 +4712,7 @@
         <v>98</v>
       </c>
       <c r="D18" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -4717,14 +4742,14 @@
         <v>95</v>
       </c>
       <c r="Q18" t="str">
-        <f>IF(NOT(ISBLANK(P18)),CONCATENATE("""^",$B$1,"/",P18,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/Dosage_.*$"</v>
       </c>
       <c r="R18" s="2">
         <v>808080</v>
       </c>
     </row>
-    <row r="19" ht="38.25">
+    <row r="19" ht="25.5">
       <c r="A19" s="2" t="s">
         <v>100</v>
       </c>
@@ -4735,7 +4760,7 @@
         <v>102</v>
       </c>
       <c r="D19" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -4761,7 +4786,7 @@
         <v>103</v>
       </c>
       <c r="Q19" t="str">
-        <f>IF(NOT(ISBLANK(P19)),CONCATENATE("""^",$B$1,"/",P19,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/Unite_.*$"</v>
       </c>
       <c r="R19" s="2">
@@ -4779,7 +4804,7 @@
         <v>106</v>
       </c>
       <c r="D20" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -4809,7 +4834,7 @@
         <v>108</v>
       </c>
       <c r="Q20" t="str">
-        <f>IF(NOT(ISBLANK(P20)),CONCATENATE("""^",$B$1,"/",P20,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/ExpressionDeDosage_.*$"</v>
       </c>
       <c r="R20" s="2">
@@ -4853,7 +4878,7 @@
       <c r="AE21" s="26"/>
       <c r="AF21" s="26"/>
     </row>
-    <row r="22" ht="38.25">
+    <row r="22" ht="25.5">
       <c r="A22" s="2" t="s">
         <v>110</v>
       </c>
@@ -4864,7 +4889,7 @@
         <v>112</v>
       </c>
       <c r="D22" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -4890,7 +4915,7 @@
         <v>113</v>
       </c>
       <c r="Q22" t="str">
-        <f>IF(NOT(ISBLANK(P22)),CONCATENATE("""^",$B$1,"/",P22,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/Organisation_.*$"</v>
       </c>
       <c r="R22" s="2" t="s">
@@ -4945,7 +4970,7 @@
         <v>118</v>
       </c>
       <c r="D24" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -4973,7 +4998,7 @@
         <v>119</v>
       </c>
       <c r="Q24" t="str">
-        <f>IF(NOT(ISBLANK(P24)),CONCATENATE("""^",$B$1,"/",P24,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/Substance_.*$"</v>
       </c>
       <c r="R24" s="2" t="s">
@@ -4981,7 +5006,7 @@
       </c>
       <c r="S24" s="2"/>
     </row>
-    <row r="25" ht="38.25">
+    <row r="25" ht="25.5">
       <c r="A25" s="2" t="s">
         <v>120</v>
       </c>
@@ -4990,7 +5015,7 @@
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="E25" s="2" t="s">
@@ -5016,7 +5041,7 @@
         <v>122</v>
       </c>
       <c r="Q25" t="str">
-        <f>IF(NOT(ISBLANK(P25)),CONCATENATE("""^",$B$1,"/",P25,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/Voie_.*$"</v>
       </c>
       <c r="R25" s="2" t="s">
@@ -5034,7 +5059,7 @@
         <v>125</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="E26" s="2" t="s">
@@ -5060,14 +5085,14 @@
         <v>126</v>
       </c>
       <c r="Q26" t="str">
-        <f>IF(NOT(ISBLANK(P26)),CONCATENATE("""^",$B$1,"/",P26,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/Forme_.*$"</v>
       </c>
       <c r="R26" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="27" ht="38.25">
+    <row r="27" ht="25.5">
       <c r="A27" s="2" t="s">
         <v>127</v>
       </c>
@@ -5076,7 +5101,7 @@
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -5102,14 +5127,14 @@
         <v>129</v>
       </c>
       <c r="Q27" t="str">
-        <f>IF(NOT(ISBLANK(P27)),CONCATENATE("""^",$B$1,"/",P27,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/UniteDePresentation_.*$"</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="28" ht="38.25">
+    <row r="28" ht="25.5">
       <c r="A28" s="2" t="s">
         <v>130</v>
       </c>
@@ -5120,7 +5145,7 @@
         <v>132</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -5146,7 +5171,7 @@
         <v>133</v>
       </c>
       <c r="Q28" t="str">
-        <f>IF(NOT(ISBLANK(P28)),CONCATENATE("""^",$B$1,"/",P28,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/Conditionnement_.*$"</v>
       </c>
       <c r="R28" s="2" t="s">
@@ -5164,7 +5189,7 @@
         <v>136</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="E29" s="2" t="s">
@@ -5190,7 +5215,7 @@
         <v>137</v>
       </c>
       <c r="Q29" t="str">
-        <f>IF(NOT(ISBLANK(P29)),CONCATENATE("""^",$B$1,"/",P29,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/JustificationNiveauVirtualisation_.*$"</v>
       </c>
       <c r="R29" s="2" t="s">
@@ -5208,7 +5233,7 @@
         <v>140</v>
       </c>
       <c r="D30" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="E30" s="2" t="s">
@@ -5234,7 +5259,7 @@
         <v>141</v>
       </c>
       <c r="Q30" t="str">
-        <f>IF(NOT(ISBLANK(P30)),CONCATENATE("""^",$B$1,"/",P30,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/JustificationNiveauPrescriptibilite_.*$"</v>
       </c>
       <c r="R30" s="2" t="s">
@@ -5252,7 +5277,7 @@
         <v>144</v>
       </c>
       <c r="D31" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -5278,7 +5303,7 @@
         <v>145</v>
       </c>
       <c r="Q31" t="str">
-        <f>IF(NOT(ISBLANK(P31)),CONCATENATE("""^",$B$1,"/",P31,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/NiveauVirtualisation_.*$"</v>
       </c>
       <c r="R31" s="2" t="s">
@@ -5296,7 +5321,7 @@
         <v>148</v>
       </c>
       <c r="D32" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -5322,14 +5347,14 @@
         <v>149</v>
       </c>
       <c r="Q32" t="str">
-        <f>IF(NOT(ISBLANK(P32)),CONCATENATE("""^",$B$1,"/",P32,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/NiveauPrescriptibilite_.*$"</v>
       </c>
       <c r="R32" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="33" ht="38.25">
+    <row r="33" ht="25.5">
       <c r="A33" s="2" t="s">
         <v>150</v>
       </c>
@@ -5340,7 +5365,7 @@
         <v>152</v>
       </c>
       <c r="D33" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="E33" s="2" t="s">
@@ -5366,14 +5391,14 @@
         <v>153</v>
       </c>
       <c r="Q33" t="str">
-        <f>IF(NOT(ISBLANK(P33)),CONCATENATE("""^",$B$1,"/",P33,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/TypeDose_.*$"</v>
       </c>
       <c r="R33" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="34" ht="38.25">
+    <row r="34" ht="25.5">
       <c r="A34" s="2" t="s">
         <v>154</v>
       </c>
@@ -5384,7 +5409,7 @@
         <v>156</v>
       </c>
       <c r="D34" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="E34" s="2" t="s">
@@ -5410,7 +5435,7 @@
         <v>157</v>
       </c>
       <c r="Q34" t="str">
-        <f>IF(NOT(ISBLANK(P34)),CONCATENATE("""^",$B$1,"/",P34,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/Gamme_.*$"</v>
       </c>
       <c r="R34" s="2" t="s">
@@ -5465,7 +5490,7 @@
         <v>161</v>
       </c>
       <c r="D36" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="E36" s="2" t="s">
@@ -5495,7 +5520,7 @@
         <v>164</v>
       </c>
       <c r="Q36" t="str">
-        <f>IF(NOT(ISBLANK(P36)),CONCATENATE("""^",$B$1,"/",P36,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/PrescriptionEnDC_.*$"</v>
       </c>
       <c r="R36" s="2" t="s">
@@ -5538,7 +5563,7 @@
       <c r="AE37" s="33"/>
       <c r="AF37" s="33"/>
     </row>
-    <row r="38" ht="38.25">
+    <row r="38" ht="25.5">
       <c r="A38" s="2" t="s">
         <v>167</v>
       </c>
@@ -5549,7 +5574,7 @@
         <v>169</v>
       </c>
       <c r="D38" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="E38" s="2" t="s">
@@ -5579,7 +5604,7 @@
         <v>172</v>
       </c>
       <c r="Q38" t="str">
-        <f>IF(NOT(ISBLANK(P38)),CONCATENATE("""^",$B$1,"/",P38,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/PPhParSubstance_.*$"</v>
       </c>
       <c r="R38" s="2" t="s">
@@ -5597,7 +5622,7 @@
         <v>176</v>
       </c>
       <c r="D39" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="E39" s="2" t="s">
@@ -5627,7 +5652,7 @@
         <v>177</v>
       </c>
       <c r="Q39" t="str">
-        <f>IF(NOT(ISBLANK(P39)),CONCATENATE("""^",$B$1,"/",P39,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/PPhParSubstanceDosage_.*$"</v>
       </c>
       <c r="R39" s="2" t="s">
@@ -5645,7 +5670,7 @@
         <v>180</v>
       </c>
       <c r="D40" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -5675,7 +5700,7 @@
         <v>181</v>
       </c>
       <c r="Q40" t="str">
-        <f>IF(NOT(ISBLANK(P40)),CONCATENATE("""^",$B$1,"/",P40,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/PPhParSubstanceForme_.*$"</v>
       </c>
       <c r="R40" s="2" t="s">
@@ -5693,7 +5718,7 @@
         <v>184</v>
       </c>
       <c r="D41" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -5723,7 +5748,7 @@
         <v>186</v>
       </c>
       <c r="Q41" t="str">
-        <f>IF(NOT(ISBLANK(P41)),CONCATENATE("""^",$B$1,"/",P41,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/PPhParSubstanceDosageForme_.*$"</v>
       </c>
       <c r="R41" s="2" t="s">
@@ -5767,7 +5792,7 @@
       <c r="AF42" s="37"/>
       <c r="AG42" s="37"/>
     </row>
-    <row r="43" ht="51">
+    <row r="43" ht="38.25">
       <c r="A43" s="2" t="s">
         <v>188</v>
       </c>
@@ -5778,7 +5803,7 @@
         <v>190</v>
       </c>
       <c r="D43" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="E43" s="2" t="s">
@@ -5800,7 +5825,7 @@
         <v>191</v>
       </c>
       <c r="Q43" t="str">
-        <f>IF(NOT(ISBLANK(P43)),CONCATENATE("""^",$B$1,"/",P43,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/Evenement_.*$"</v>
       </c>
       <c r="R43" s="2" t="s">
@@ -5818,7 +5843,7 @@
         <v>195</v>
       </c>
       <c r="D44" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="E44" s="2" t="s">
@@ -5831,7 +5856,7 @@
       <c r="H44" s="8"/>
       <c r="I44" s="9"/>
       <c r="J44" s="10"/>
-      <c r="M44" s="8" t="s">
+      <c r="K44" s="8" t="s">
         <v>197</v>
       </c>
       <c r="N44" s="8" t="s">
@@ -5844,7 +5869,7 @@
         <v>198</v>
       </c>
       <c r="Q44" t="str">
-        <f>IF(NOT(ISBLANK(P44)),CONCATENATE("""^",$B$1,"/",P44,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/Autorisation_.*$"</v>
       </c>
       <c r="R44" s="2" t="s">
@@ -5862,7 +5887,7 @@
         <v>201</v>
       </c>
       <c r="D45" s="40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="E45" s="39" t="s">
@@ -5873,8 +5898,7 @@
       <c r="H45" s="40"/>
       <c r="I45" s="41"/>
       <c r="J45" s="42"/>
-      <c r="K45" s="39"/>
-      <c r="M45" s="40" t="s">
+      <c r="K45" s="40" t="s">
         <v>197</v>
       </c>
       <c r="N45" s="40" t="s">
@@ -5887,14 +5911,14 @@
         <v>202</v>
       </c>
       <c r="Q45" s="39" t="str">
-        <f>IF(NOT(ISBLANK(P45)),CONCATENATE("""^",$B$1,"/",P45,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/AccesDerogatoire_.*$"</v>
       </c>
       <c r="R45" s="39" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="46" ht="38.25">
+    <row r="46" ht="25.5">
       <c r="A46" s="2" t="s">
         <v>203</v>
       </c>
@@ -5905,7 +5929,7 @@
         <v>205</v>
       </c>
       <c r="D46" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="E46" s="2" t="s">
@@ -5916,7 +5940,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="9"/>
       <c r="J46" s="10"/>
-      <c r="M46" s="8" t="s">
+      <c r="K46" s="8" t="s">
         <v>197</v>
       </c>
       <c r="N46" s="8" t="s">
@@ -5929,7 +5953,7 @@
         <v>206</v>
       </c>
       <c r="Q46" t="str">
-        <f>IF(NOT(ISBLANK(P46)),CONCATENATE("""^",$B$1,"/",P46,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/ChangementDeStatut_.*$"</v>
       </c>
       <c r="R46" s="2" t="s">
@@ -5983,7 +6007,7 @@
         <v>210</v>
       </c>
       <c r="D48" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="E48" s="2" t="s">
@@ -6009,14 +6033,14 @@
         <v>211</v>
       </c>
       <c r="Q48" t="str">
-        <f>IF(NOT(ISBLANK(P48)),CONCATENATE("""^",$B$1,"/",P48,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/TypeProcedure_.*$"</v>
       </c>
       <c r="R48" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="49" ht="38.25">
+    <row r="49" ht="25.5">
       <c r="A49" s="2" t="s">
         <v>212</v>
       </c>
@@ -6027,7 +6051,7 @@
         <v>214</v>
       </c>
       <c r="D49" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="E49" s="2" t="s">
@@ -6053,14 +6077,14 @@
         <v>215</v>
       </c>
       <c r="Q49" t="str">
-        <f>IF(NOT(ISBLANK(P49)),CONCATENATE("""^",$B$1,"/",P49,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/StatutSpecialite_.*$"</v>
       </c>
       <c r="R49" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="50" ht="38.25">
+    <row r="50" ht="25.5">
       <c r="A50" s="2" t="s">
         <v>216</v>
       </c>
@@ -6071,7 +6095,7 @@
         <v>218</v>
       </c>
       <c r="D50" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="E50" s="2" t="s">
@@ -6097,7 +6121,7 @@
         <v>219</v>
       </c>
       <c r="Q50" t="str">
-        <f>IF(NOT(ISBLANK(P50)),CONCATENATE("""^",$B$1,"/",P50,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v>"^http://data.esante.gouv.fr/ansm/medicament/TypeEvenement_.*$"</v>
       </c>
       <c r="R50" s="2" t="s">
@@ -6152,7 +6176,7 @@
         <v>223</v>
       </c>
       <c r="D52" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="E52" s="2" t="s">
@@ -6174,7 +6198,7 @@
         <v>224</v>
       </c>
       <c r="Q52" t="str">
-        <f>IF(NOT(ISBLANK(P52)),CONCATENATE("""^",$B$1,"/",P52,"$"""),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -13410,7 +13434,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="57" t="str">
-        <f t="shared" ref="M11:M74" si="1">IF(K11&lt;&gt;"",IF(OR(LEFT(K11,3)="rdf",LEFT(K11,3)="xsd",LEFT(K11,3)="cdt"),K11,""),"")</f>
+        <f t="shared" ref="M11:M74" si="2">IF(K11&lt;&gt;"",IF(OR(LEFT(K11,3)="rdf",LEFT(K11,3)="xsd",LEFT(K11,3)="cdt"),K11,""),"")</f>
         <v>xsd:string</v>
       </c>
       <c r="N11" s="45"/>
@@ -13419,7 +13443,7 @@
       <c r="Q11" s="8"/>
       <c r="R11" s="2"/>
       <c r="T11" t="str">
-        <f t="shared" ref="T11:T74" si="2">IF(D11=TRUE,"#EAF1DD","")</f>
+        <f t="shared" ref="T11:T74" si="3">IF(D11=TRUE,"#EAF1DD","")</f>
         <v/>
       </c>
     </row>
@@ -13456,15 +13480,15 @@
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>rdf:langString</v>
       </c>
       <c r="N12" s="45" t="str">
-        <f t="shared" ref="N12:N75" si="3">IF(K12&lt;&gt;"",IF(AND(M12="",LEFT(K12,13)&lt;&gt;"med:BlankNode"),K12,""),"")</f>
+        <f t="shared" ref="N12:N75" si="4">IF(K12&lt;&gt;"",IF(AND(M12="",LEFT(K12,13)&lt;&gt;"med:BlankNode"),K12,""),"")</f>
         <v/>
       </c>
       <c r="O12" s="45" t="str">
-        <f t="shared" ref="O12:O75" si="4">IF(K12&lt;&gt;"",IF(AND(M12="",LEFT(K12,13)="med:BlankNode"),K12,""),"")</f>
+        <f t="shared" ref="O12:O75" si="5">IF(K12&lt;&gt;"",IF(AND(M12="",LEFT(K12,13)="med:BlankNode"),K12,""),"")</f>
         <v/>
       </c>
       <c r="P12" s="8" t="s">
@@ -13475,7 +13499,7 @@
         <v>271</v>
       </c>
       <c r="T12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13510,21 +13534,21 @@
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N13" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:Substance</v>
       </c>
       <c r="O13" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
       <c r="T13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13595,7 +13619,7 @@
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:string</v>
       </c>
       <c r="N15" s="45"/>
@@ -13604,7 +13628,7 @@
       <c r="Q15" s="8"/>
       <c r="R15" s="2"/>
       <c r="T15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13641,15 +13665,15 @@
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>rdf:langString</v>
       </c>
       <c r="N16" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O16" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P16" s="8" t="s">
@@ -13660,7 +13684,7 @@
         <v>271</v>
       </c>
       <c r="T16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13695,21 +13719,21 @@
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N17" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:Substance</v>
       </c>
       <c r="O17" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
       <c r="T17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13742,21 +13766,21 @@
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N18" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:DosagePresentation</v>
       </c>
       <c r="O18" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
       <c r="T18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13789,21 +13813,21 @@
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N19" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:DosageConcentration</v>
       </c>
       <c r="O19" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
       <c r="T19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13840,21 +13864,21 @@
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N20" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:PPhParSubstance</v>
       </c>
       <c r="O20" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
       <c r="T20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13925,7 +13949,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:string</v>
       </c>
       <c r="N22" s="45"/>
@@ -13934,7 +13958,7 @@
       <c r="Q22" s="8"/>
       <c r="R22" s="2"/>
       <c r="T22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -13971,15 +13995,15 @@
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>rdf:langString</v>
       </c>
       <c r="N23" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O23" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P23" s="8" t="s">
@@ -13990,7 +14014,7 @@
         <v>271</v>
       </c>
       <c r="T23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14025,21 +14049,21 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N24" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:Substance</v>
       </c>
       <c r="O24" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
       <c r="T24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14076,21 +14100,21 @@
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N25" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:Forme</v>
       </c>
       <c r="O25" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
       <c r="T25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14127,21 +14151,21 @@
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N26" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:PPhParSubstance</v>
       </c>
       <c r="O26" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
       <c r="T26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14212,7 +14236,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:string</v>
       </c>
       <c r="N28" s="45"/>
@@ -14221,7 +14245,7 @@
       <c r="Q28" s="8"/>
       <c r="R28" s="2"/>
       <c r="T28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14258,15 +14282,15 @@
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>rdf:langString</v>
       </c>
       <c r="N29" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O29" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P29" s="8" t="s">
@@ -14277,7 +14301,7 @@
         <v>271</v>
       </c>
       <c r="T29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14312,21 +14336,21 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N30" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:Substance</v>
       </c>
       <c r="O30" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
       <c r="T30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14359,21 +14383,21 @@
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N31" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:DosagePresentation</v>
       </c>
       <c r="O31" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
       <c r="T31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14406,21 +14430,21 @@
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N32" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:DosageConcentration</v>
       </c>
       <c r="O32" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
       <c r="T32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14457,21 +14481,21 @@
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N33" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:Forme</v>
       </c>
       <c r="O33" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P33" s="8"/>
       <c r="Q33" s="8"/>
       <c r="T33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14508,22 +14532,22 @@
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N34" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:PPhParSubstanceDosage</v>
       </c>
       <c r="O34" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P34" s="8"/>
       <c r="Q34" s="8"/>
       <c r="R34" s="2"/>
       <c r="T34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14560,22 +14584,22 @@
       </c>
       <c r="L35" s="2"/>
       <c r="M35" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N35" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:PPhParSubstanceForme</v>
       </c>
       <c r="O35" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P35" s="8"/>
       <c r="Q35" s="8"/>
       <c r="R35" s="2"/>
       <c r="T35" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14646,7 +14670,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:string</v>
       </c>
       <c r="N37" s="45"/>
@@ -14655,7 +14679,7 @@
       <c r="Q37" s="8"/>
       <c r="R37" s="2"/>
       <c r="T37" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14692,15 +14716,15 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>rdf:langString</v>
       </c>
       <c r="N38" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O38" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P38" s="8" t="s">
@@ -14711,7 +14735,7 @@
         <v>271</v>
       </c>
       <c r="T38" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14746,21 +14770,21 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:date</v>
       </c>
       <c r="N39" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O39" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P39" s="8"/>
       <c r="Q39" s="8"/>
       <c r="T39" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14795,22 +14819,22 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:date</v>
       </c>
       <c r="N40" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O40" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P40" s="8"/>
       <c r="Q40" s="8"/>
       <c r="R40" s="2"/>
       <c r="T40" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14847,21 +14871,21 @@
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:boolean</v>
       </c>
       <c r="N41" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O41" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P41" s="8"/>
       <c r="Q41" s="8"/>
       <c r="T41" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14900,21 +14924,21 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N42" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:Substance</v>
       </c>
       <c r="O42" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
       <c r="T42" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14949,21 +14973,21 @@
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N43" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:DosagePresentation</v>
       </c>
       <c r="O43" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P43" s="8"/>
       <c r="Q43" s="8"/>
       <c r="T43" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -14998,21 +15022,21 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N44" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:DosageConcentration</v>
       </c>
       <c r="O44" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P44" s="8"/>
       <c r="Q44" s="8"/>
       <c r="T44" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15049,22 +15073,22 @@
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N45" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:Forme</v>
       </c>
       <c r="O45" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P45" s="8"/>
       <c r="Q45" s="8"/>
       <c r="R45" s="2"/>
       <c r="T45" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15101,21 +15125,21 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N46" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:Voie</v>
       </c>
       <c r="O46" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P46" s="8"/>
       <c r="Q46" s="8"/>
       <c r="T46" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15152,22 +15176,22 @@
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N47" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:UniteDePresentation</v>
       </c>
       <c r="O47" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P47" s="8"/>
       <c r="Q47" s="8"/>
       <c r="R47" s="2"/>
       <c r="T47" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15200,21 +15224,21 @@
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N48" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O48" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P48" s="8"/>
       <c r="Q48" s="8"/>
       <c r="T48" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15251,21 +15275,21 @@
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N49" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:PPhParSubstanceDosageForme</v>
       </c>
       <c r="O49" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P49" s="8"/>
       <c r="Q49" s="8"/>
       <c r="T49" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15340,15 +15364,15 @@
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>rdf:langString</v>
       </c>
       <c r="N51" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O51" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P51" s="8" t="s">
@@ -15356,7 +15380,7 @@
       </c>
       <c r="Q51" s="8"/>
       <c r="T51" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15393,21 +15417,21 @@
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N52" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:Substance</v>
       </c>
       <c r="O52" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P52" s="8"/>
       <c r="Q52" s="8"/>
       <c r="T52" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15442,21 +15466,21 @@
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:decimal</v>
       </c>
       <c r="N53" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O53" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P53" s="8"/>
       <c r="Q53" s="8"/>
       <c r="T53" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15491,21 +15515,21 @@
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>cdt:ucumunit</v>
       </c>
       <c r="N54" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O54" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P54" s="8"/>
       <c r="Q54" s="8"/>
       <c r="T54" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15540,18 +15564,18 @@
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:decimal</v>
       </c>
       <c r="N55" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O55" s="45"/>
       <c r="P55" s="8"/>
       <c r="Q55" s="8"/>
       <c r="T55" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15586,18 +15610,18 @@
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>cdt:ucumunit</v>
       </c>
       <c r="N56" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O56" s="45"/>
       <c r="P56" s="8"/>
       <c r="Q56" s="8"/>
       <c r="T56" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15632,18 +15656,18 @@
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:decimal</v>
       </c>
       <c r="N57" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O57" s="45"/>
       <c r="P57" s="8"/>
       <c r="Q57" s="8"/>
       <c r="T57" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15678,18 +15702,18 @@
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>cdt:ucumunit</v>
       </c>
       <c r="N58" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O58" s="45"/>
       <c r="P58" s="8"/>
       <c r="Q58" s="8"/>
       <c r="T58" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15726,21 +15750,21 @@
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:decimal</v>
       </c>
       <c r="N59" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O59" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P59" s="8"/>
       <c r="Q59" s="8"/>
       <c r="T59" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15775,21 +15799,21 @@
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>cdt:ucumunit</v>
       </c>
       <c r="N60" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O60" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
       <c r="T60" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15826,21 +15850,21 @@
       </c>
       <c r="L61" s="64"/>
       <c r="M61" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N61" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:UniteDePresentation</v>
       </c>
       <c r="O61" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P61" s="8"/>
       <c r="Q61" s="8"/>
       <c r="T61" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15915,15 +15939,15 @@
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>rdf:langString</v>
       </c>
       <c r="N63" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O63" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P63" s="8" t="s">
@@ -15931,7 +15955,7 @@
       </c>
       <c r="Q63" s="8"/>
       <c r="T63" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -15968,21 +15992,21 @@
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="N64" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>med:Substance</v>
       </c>
       <c r="O64" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P64" s="8"/>
       <c r="Q64" s="8"/>
       <c r="T64" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -16019,21 +16043,21 @@
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:decimal</v>
       </c>
       <c r="N65" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O65" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P65" s="8"/>
       <c r="Q65" s="8"/>
       <c r="T65" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -16068,18 +16092,18 @@
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:decimal</v>
       </c>
       <c r="N66" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O66" s="45"/>
       <c r="P66" s="8"/>
       <c r="Q66" s="8"/>
       <c r="T66" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -16114,18 +16138,18 @@
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>cdt:ucumunit</v>
       </c>
       <c r="N67" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O67" s="45"/>
       <c r="P67" s="8"/>
       <c r="Q67" s="8"/>
       <c r="T67" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -16160,18 +16184,18 @@
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:decimal</v>
       </c>
       <c r="N68" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O68" s="45"/>
       <c r="P68" s="8"/>
       <c r="Q68" s="8"/>
       <c r="T68" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -16206,18 +16230,18 @@
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>cdt:ucumunit</v>
       </c>
       <c r="N69" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O69" s="45"/>
       <c r="P69" s="8"/>
       <c r="Q69" s="8"/>
       <c r="T69" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -16254,21 +16278,21 @@
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>cdt:ucumunit</v>
       </c>
       <c r="N70" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O70" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P70" s="8"/>
       <c r="Q70" s="8"/>
       <c r="T70" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -16303,21 +16327,21 @@
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>xsd:boolean</v>
       </c>
       <c r="N71" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O71" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P71" s="8"/>
       <c r="Q71" s="8"/>
       <c r="T71" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -16392,15 +16416,15 @@
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>rdf:langString</v>
       </c>
       <c r="N73" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O73" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P73" s="8" t="s">
@@ -16408,7 +16432,7 @@
       </c>
       <c r="Q73" s="8"/>
       <c r="T73" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -16445,21 +16469,21 @@
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>cdt:ucumunit</v>
       </c>
       <c r="N74" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O74" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P74" s="8"/>
       <c r="Q74" s="8"/>
       <c r="T74" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -16494,21 +16518,21 @@
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="57" t="str">
-        <f t="shared" ref="M75:M100" si="5">IF(K75&lt;&gt;"",IF(OR(LEFT(K75,3)="rdf",LEFT(K75,3)="xsd",LEFT(K75,3)="cdt"),K75,""),"")</f>
+        <f t="shared" ref="M75:M100" si="6">IF(K75&lt;&gt;"",IF(OR(LEFT(K75,3)="rdf",LEFT(K75,3)="xsd",LEFT(K75,3)="cdt"),K75,""),"")</f>
         <v>xsd:decimal</v>
       </c>
       <c r="N75" s="45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O75" s="45" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="P75" s="8"/>
       <c r="Q75" s="8"/>
       <c r="T75" t="str">
-        <f t="shared" ref="T75:T138" si="6">IF(D75=TRUE,"#EAF1DD","")</f>
+        <f t="shared" ref="T75:T138" si="7">IF(D75=TRUE,"#EAF1DD","")</f>
         <v/>
       </c>
     </row>
@@ -16539,21 +16563,21 @@
         <v>58</v>
       </c>
       <c r="M76" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N76" s="45" t="str">
-        <f t="shared" ref="N76:N100" si="7">IF(K76&lt;&gt;"",IF(AND(M76="",LEFT(K76,13)&lt;&gt;"med:BlankNode"),K76,""),"")</f>
+        <f t="shared" ref="N76:N100" si="8">IF(K76&lt;&gt;"",IF(AND(M76="",LEFT(K76,13)&lt;&gt;"med:BlankNode"),K76,""),"")</f>
         <v/>
       </c>
       <c r="O76" s="45" t="str">
-        <f t="shared" ref="O76:O100" si="8">IF(K76&lt;&gt;"",IF(AND(M76="",LEFT(K76,13)="med:BlankNode"),K76,""),"")</f>
+        <f t="shared" ref="O76:O100" si="9">IF(K76&lt;&gt;"",IF(AND(M76="",LEFT(K76,13)="med:BlankNode"),K76,""),"")</f>
         <v/>
       </c>
       <c r="P76" s="8"/>
       <c r="Q76" s="8"/>
       <c r="T76" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -16628,15 +16652,15 @@
       </c>
       <c r="L78" s="8"/>
       <c r="M78" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>xsd:string</v>
       </c>
       <c r="N78" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O78" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P78" s="8"/>
@@ -16644,7 +16668,7 @@
       <c r="R78" s="8"/>
       <c r="S78" s="8"/>
       <c r="T78" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U78" s="8"/>
@@ -16695,15 +16719,15 @@
       </c>
       <c r="L79" s="8"/>
       <c r="M79" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>rdf:langString</v>
       </c>
       <c r="N79" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O79" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P79" s="8" t="s">
@@ -16715,7 +16739,7 @@
       </c>
       <c r="S79" s="8"/>
       <c r="T79" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U79" s="8"/>
@@ -16764,15 +16788,15 @@
       </c>
       <c r="L80" s="8"/>
       <c r="M80" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>xsd:boolean</v>
       </c>
       <c r="N80" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O80" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P80" s="8"/>
@@ -16780,7 +16804,7 @@
       <c r="R80" s="8"/>
       <c r="S80" s="8"/>
       <c r="T80" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U80" s="8"/>
@@ -16831,15 +16855,15 @@
       </c>
       <c r="L81" s="8"/>
       <c r="M81" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>xsd:date</v>
       </c>
       <c r="N81" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O81" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P81" s="8"/>
@@ -16847,7 +16871,7 @@
       <c r="R81" s="8"/>
       <c r="S81" s="8"/>
       <c r="T81" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U81" s="8"/>
@@ -16896,15 +16920,15 @@
       </c>
       <c r="L82" s="8"/>
       <c r="M82" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>xsd:date</v>
       </c>
       <c r="N82" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O82" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P82" s="8"/>
@@ -16912,7 +16936,7 @@
       <c r="R82" s="8"/>
       <c r="S82" s="8"/>
       <c r="T82" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U82" s="8"/>
@@ -16959,15 +16983,15 @@
       <c r="K83" s="70"/>
       <c r="L83" s="70"/>
       <c r="M83" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N83" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O83" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P83" s="8"/>
@@ -16975,7 +16999,7 @@
       <c r="R83" s="8"/>
       <c r="S83" s="8"/>
       <c r="T83" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U83" s="8"/>
@@ -17026,15 +17050,15 @@
       </c>
       <c r="L84" s="70"/>
       <c r="M84" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>xsd:string</v>
       </c>
       <c r="N84" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O84" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P84" s="8"/>
@@ -17042,7 +17066,7 @@
       <c r="R84" s="8"/>
       <c r="S84" s="8"/>
       <c r="T84" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U84" s="8"/>
@@ -17093,15 +17117,15 @@
       </c>
       <c r="L85" s="70"/>
       <c r="M85" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>rdf:langString</v>
       </c>
       <c r="N85" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O85" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P85" s="8"/>
@@ -17109,7 +17133,7 @@
       <c r="R85" s="8"/>
       <c r="S85" s="8"/>
       <c r="T85" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U85" s="8"/>
@@ -17156,15 +17180,15 @@
       </c>
       <c r="L86" s="8"/>
       <c r="M86" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N86" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>med:Evenement</v>
       </c>
       <c r="O86" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P86" s="8"/>
@@ -17172,7 +17196,7 @@
       <c r="R86" s="8"/>
       <c r="S86" s="8"/>
       <c r="T86" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U86" s="8"/>
@@ -17223,15 +17247,15 @@
       </c>
       <c r="L87" s="8"/>
       <c r="M87" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N87" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>med:TypeProcedure</v>
       </c>
       <c r="O87" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P87" s="8"/>
@@ -17239,7 +17263,7 @@
       <c r="R87" s="8"/>
       <c r="S87" s="8"/>
       <c r="T87" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U87" s="8"/>
@@ -17290,15 +17314,15 @@
       </c>
       <c r="L88" s="8"/>
       <c r="M88" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N88" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>med:StatutSpecialite</v>
       </c>
       <c r="O88" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P88" s="8"/>
@@ -17306,7 +17330,7 @@
       <c r="R88" s="8"/>
       <c r="S88" s="8"/>
       <c r="T88" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U88" s="8"/>
@@ -17353,21 +17377,21 @@
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N89" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>med:Element</v>
       </c>
       <c r="O89" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P89" s="8"/>
       <c r="Q89" s="8"/>
       <c r="T89" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -17406,21 +17430,21 @@
         <v>436</v>
       </c>
       <c r="M90" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N90" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>med:Substance</v>
       </c>
       <c r="O90" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P90" s="8"/>
       <c r="Q90" s="8"/>
       <c r="T90" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -17454,21 +17478,21 @@
         <v>116</v>
       </c>
       <c r="M91" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N91" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>med:Substance</v>
       </c>
       <c r="O91" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P91" s="8"/>
       <c r="Q91" s="8"/>
       <c r="T91" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -17507,21 +17531,21 @@
         <v>436</v>
       </c>
       <c r="M92" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N92" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>med:Substance</v>
       </c>
       <c r="O92" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P92" s="8"/>
       <c r="Q92" s="8"/>
       <c r="T92" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -17560,21 +17584,21 @@
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N93" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>med:Forme</v>
       </c>
       <c r="O93" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P93" s="8"/>
       <c r="Q93" s="8"/>
       <c r="T93" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -17611,21 +17635,21 @@
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>xsd:boolean</v>
       </c>
       <c r="N94" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O94" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P94" s="8"/>
       <c r="Q94" s="8"/>
       <c r="T94" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -17662,21 +17686,21 @@
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N95" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>med:UniteCommuneDeDispensation</v>
       </c>
       <c r="O95" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P95" s="8"/>
       <c r="Q95" s="8"/>
       <c r="T95" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -17713,21 +17737,21 @@
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N96" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>med:Presentation</v>
       </c>
       <c r="O96" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P96" s="8"/>
       <c r="Q96" s="8"/>
       <c r="T96" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -17760,15 +17784,15 @@
       </c>
       <c r="L97" s="71"/>
       <c r="M97" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N97" s="57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O97" s="57" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>med:BlankNode_LabelWithDates</v>
       </c>
       <c r="P97" s="71"/>
@@ -17776,7 +17800,7 @@
       <c r="R97" s="71"/>
       <c r="S97" s="71"/>
       <c r="T97" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="U97" s="71"/>
@@ -17825,15 +17849,15 @@
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="71" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N98" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>med:NiveauVirtualisation</v>
       </c>
       <c r="O98" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P98" s="8"/>
@@ -17841,7 +17865,7 @@
       <c r="R98" s="8"/>
       <c r="S98" s="8"/>
       <c r="T98" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="U98" s="8"/>
@@ -17892,15 +17916,15 @@
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="71" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N99" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>med:NiveauPrescriptibilite</v>
       </c>
       <c r="O99" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P99" s="8"/>
@@ -17908,7 +17932,7 @@
       <c r="R99" s="8"/>
       <c r="S99" s="8"/>
       <c r="T99" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U99" s="8"/>
@@ -17953,21 +17977,21 @@
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="N100" s="45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>med:JustificationNiveauVirtualisation</v>
       </c>
       <c r="O100" s="45" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P100" s="8"/>
       <c r="Q100" s="8"/>
       <c r="T100" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -18002,21 +18026,21 @@
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="57" t="str">
-        <f t="shared" ref="M101:M164" si="9">IF(K101&lt;&gt;"",IF(OR(LEFT(K101,3)="rdf",LEFT(K101,3)="xsd",LEFT(K101,3)="cdt"),K101,""),"")</f>
+        <f t="shared" ref="M101:M164" si="10">IF(K101&lt;&gt;"",IF(OR(LEFT(K101,3)="rdf",LEFT(K101,3)="xsd",LEFT(K101,3)="cdt"),K101,""),"")</f>
         <v/>
       </c>
       <c r="N101" s="45" t="str">
-        <f t="shared" ref="N101:N164" si="10">IF(K101&lt;&gt;"",IF(AND(M101="",LEFT(K101,13)&lt;&gt;"med:BlankNode"),K101,""),"")</f>
+        <f t="shared" ref="N101:N164" si="11">IF(K101&lt;&gt;"",IF(AND(M101="",LEFT(K101,13)&lt;&gt;"med:BlankNode"),K101,""),"")</f>
         <v>med:JustificationNiveauPrescriptibilite</v>
       </c>
       <c r="O101" s="45" t="str">
-        <f t="shared" ref="O101:O164" si="11">IF(K101&lt;&gt;"",IF(AND(M101="",LEFT(K101,13)="med:BlankNode"),K101,""),"")</f>
+        <f t="shared" ref="O101:O164" si="12">IF(K101&lt;&gt;"",IF(AND(M101="",LEFT(K101,13)="med:BlankNode"),K101,""),"")</f>
         <v/>
       </c>
       <c r="P101" s="8"/>
       <c r="Q101" s="8"/>
       <c r="T101" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -18055,21 +18079,21 @@
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N102" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Organisation</v>
       </c>
       <c r="O102" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P102" s="8"/>
       <c r="Q102" s="8"/>
       <c r="T102" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -18106,21 +18130,21 @@
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N103" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Voie</v>
       </c>
       <c r="O103" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P103" s="8"/>
       <c r="Q103" s="8"/>
       <c r="T103" s="8" t="str">
-        <f t="shared" ref="T103:T107" si="12">IF(D103=TRUE,"#EAF1DD","")</f>
+        <f t="shared" ref="T103:T107" si="13">IF(D103=TRUE,"#EAF1DD","")</f>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -18155,15 +18179,15 @@
       </c>
       <c r="L104" s="8"/>
       <c r="M104" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N104" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:GroupeGenerique</v>
       </c>
       <c r="O104" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P104" s="8"/>
@@ -18171,7 +18195,7 @@
       <c r="R104" s="8"/>
       <c r="S104" s="8"/>
       <c r="T104" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U104" s="8"/>
@@ -18218,15 +18242,15 @@
       </c>
       <c r="L105" s="8"/>
       <c r="M105" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N105" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:GroupeGenerique</v>
       </c>
       <c r="O105" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P105" s="8"/>
@@ -18234,7 +18258,7 @@
       <c r="R105" s="8"/>
       <c r="S105" s="8"/>
       <c r="T105" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U105" s="8"/>
@@ -18281,15 +18305,15 @@
       </c>
       <c r="L106" s="8"/>
       <c r="M106" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N106" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:GroupeGenerique</v>
       </c>
       <c r="O106" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P106" s="8"/>
@@ -18297,7 +18321,7 @@
       <c r="R106" s="8"/>
       <c r="S106" s="8"/>
       <c r="T106" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U106" s="8"/>
@@ -18348,15 +18372,15 @@
       </c>
       <c r="L107" s="8"/>
       <c r="M107" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N107" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Gamme</v>
       </c>
       <c r="O107" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P107" s="8"/>
@@ -18364,7 +18388,7 @@
       <c r="R107" s="8"/>
       <c r="S107" s="8"/>
       <c r="T107" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U107" s="8"/>
@@ -18451,15 +18475,15 @@
       </c>
       <c r="L109" s="8"/>
       <c r="M109" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:string</v>
       </c>
       <c r="N109" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O109" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P109" s="8"/>
@@ -18467,7 +18491,7 @@
       <c r="R109" s="8"/>
       <c r="S109" s="8"/>
       <c r="T109" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U109" s="8"/>
@@ -18518,15 +18542,15 @@
       </c>
       <c r="L110" s="8"/>
       <c r="M110" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>rdf:langString</v>
       </c>
       <c r="N110" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O110" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P110" s="8" t="s">
@@ -18536,7 +18560,7 @@
       <c r="R110" s="8"/>
       <c r="S110" s="8"/>
       <c r="T110" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U110" s="8"/>
@@ -18587,15 +18611,15 @@
         <v>436</v>
       </c>
       <c r="M111" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N111" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:ExpressionDeDosage</v>
       </c>
       <c r="O111" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P111" s="8"/>
@@ -18603,7 +18627,7 @@
       <c r="R111" s="8"/>
       <c r="S111" s="8"/>
       <c r="T111" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U111" s="8"/>
@@ -18654,15 +18678,15 @@
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N112" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:SpecialitePharmaceutique</v>
       </c>
       <c r="O112" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P112" s="8"/>
@@ -18670,7 +18694,7 @@
       <c r="R112" s="8"/>
       <c r="S112" s="8"/>
       <c r="T112" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U112" s="8"/>
@@ -18721,15 +18745,15 @@
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:string</v>
       </c>
       <c r="N113" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O113" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P113" s="8"/>
@@ -18737,7 +18761,7 @@
       <c r="R113" s="8"/>
       <c r="S113" s="8"/>
       <c r="T113" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U113" s="8"/>
@@ -18786,15 +18810,15 @@
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N114" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Forme</v>
       </c>
       <c r="O114" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P114" s="8"/>
@@ -18802,7 +18826,7 @@
       <c r="R114" s="8"/>
       <c r="S114" s="8"/>
       <c r="T114" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="U114" s="8"/>
@@ -18853,21 +18877,21 @@
         <v>436</v>
       </c>
       <c r="M115" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N115" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Substance</v>
       </c>
       <c r="O115" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P115" s="8"/>
       <c r="Q115" s="8"/>
       <c r="T115" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -18901,21 +18925,21 @@
         <v>116</v>
       </c>
       <c r="M116" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N116" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Substance</v>
       </c>
       <c r="O116" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P116" s="8"/>
       <c r="Q116" s="8"/>
       <c r="T116" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -18954,21 +18978,21 @@
         <v>436</v>
       </c>
       <c r="M117" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N117" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Substance</v>
       </c>
       <c r="O117" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P117" s="8"/>
       <c r="Q117" s="8"/>
       <c r="T117" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -19005,15 +19029,15 @@
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N118" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:DosageConcentration</v>
       </c>
       <c r="O118" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P118" s="8"/>
@@ -19021,7 +19045,7 @@
       <c r="R118" s="8"/>
       <c r="S118" s="8"/>
       <c r="T118" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="U118" s="8"/>
@@ -19070,15 +19094,15 @@
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N119" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:ElementPresentation</v>
       </c>
       <c r="O119" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P119" s="8"/>
@@ -19086,7 +19110,7 @@
       <c r="R119" s="8"/>
       <c r="S119" s="8"/>
       <c r="T119" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="U119" s="8"/>
@@ -19173,15 +19197,15 @@
       </c>
       <c r="L121" s="8"/>
       <c r="M121" s="71" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>rdf:langString</v>
       </c>
       <c r="N121" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O121" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P121" s="8" t="s">
@@ -19191,7 +19215,7 @@
       <c r="R121" s="8"/>
       <c r="S121" s="8"/>
       <c r="T121" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U121" s="8"/>
@@ -19242,21 +19266,21 @@
       </c>
       <c r="L122" s="2"/>
       <c r="M122" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N122" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Substance</v>
       </c>
       <c r="O122" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P122" s="8"/>
       <c r="Q122" s="8"/>
       <c r="T122" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -19295,21 +19319,21 @@
       </c>
       <c r="L123" s="2"/>
       <c r="M123" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:string</v>
       </c>
       <c r="N123" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O123" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P123" s="8"/>
       <c r="Q123" s="8"/>
       <c r="T123" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -19348,21 +19372,21 @@
       </c>
       <c r="L124" s="2"/>
       <c r="M124" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:string</v>
       </c>
       <c r="N124" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O124" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P124" s="8"/>
       <c r="Q124" s="8"/>
       <c r="T124" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -19403,21 +19427,21 @@
         <v>436</v>
       </c>
       <c r="M125" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:string</v>
       </c>
       <c r="N125" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O125" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P125" s="8"/>
       <c r="Q125" s="8"/>
       <c r="T125" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -19456,21 +19480,21 @@
       </c>
       <c r="L126" s="2"/>
       <c r="M126" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:string</v>
       </c>
       <c r="N126" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O126" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P126" s="8"/>
       <c r="Q126" s="8"/>
       <c r="T126" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -19509,21 +19533,21 @@
         <v>436</v>
       </c>
       <c r="M127" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N127" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Substance</v>
       </c>
       <c r="O127" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P127" s="8"/>
       <c r="Q127" s="8"/>
       <c r="T127" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -19557,21 +19581,21 @@
         <v>116</v>
       </c>
       <c r="M128" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N128" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Substance</v>
       </c>
       <c r="O128" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P128" s="8"/>
       <c r="Q128" s="8"/>
       <c r="T128" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -19591,7 +19615,7 @@
       <c r="K129" s="65"/>
       <c r="L129" s="65"/>
       <c r="M129" s="65" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N129" s="65"/>
@@ -19649,7 +19673,7 @@
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:string</v>
       </c>
       <c r="N130" s="45"/>
@@ -19658,7 +19682,7 @@
       <c r="Q130" s="8"/>
       <c r="R130" s="2"/>
       <c r="T130" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -19697,15 +19721,15 @@
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>rdf:langString</v>
       </c>
       <c r="N131" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O131" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P131" s="8" t="s">
@@ -19713,7 +19737,7 @@
       </c>
       <c r="Q131" s="8"/>
       <c r="T131" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -19748,21 +19772,21 @@
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N132" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:SpecialitePharmaceutique</v>
       </c>
       <c r="O132" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P132" s="8"/>
       <c r="Q132" s="8"/>
       <c r="T132" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -19797,21 +19821,21 @@
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N133" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:SpecialitePharmaceutique</v>
       </c>
       <c r="O133" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P133" s="8"/>
       <c r="Q133" s="8"/>
       <c r="T133" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -19846,21 +19870,21 @@
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N134" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:SpecialitePharmaceutique</v>
       </c>
       <c r="O134" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P134" s="8"/>
       <c r="Q134" s="8"/>
       <c r="T134" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -19935,21 +19959,21 @@
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:string</v>
       </c>
       <c r="N136" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O136" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P136" s="8"/>
       <c r="Q136" s="8"/>
       <c r="T136" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -19988,21 +20012,21 @@
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:string</v>
       </c>
       <c r="N137" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O137" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P137" s="8"/>
       <c r="Q137" s="8"/>
       <c r="T137" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20041,15 +20065,15 @@
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>rdf:langString</v>
       </c>
       <c r="N138" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O138" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P138" s="8" t="s">
@@ -20057,7 +20081,7 @@
       </c>
       <c r="Q138" s="8"/>
       <c r="T138" s="8" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20096,21 +20120,21 @@
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N139" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:SpecialitePharmaceutique</v>
       </c>
       <c r="O139" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P139" s="8"/>
       <c r="Q139" s="8"/>
       <c r="T139" s="8" t="str">
-        <f t="shared" ref="T139:T202" si="13">IF(D139=TRUE,"#EAF1DD","")</f>
+        <f t="shared" ref="T139:T202" si="14">IF(D139=TRUE,"#EAF1DD","")</f>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20147,21 +20171,21 @@
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N140" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Presentation</v>
       </c>
       <c r="O140" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P140" s="8"/>
       <c r="Q140" s="8"/>
       <c r="T140" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20195,21 +20219,21 @@
       </c>
       <c r="L141" s="64"/>
       <c r="M141" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N141" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O141" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>med:BlankNode_LabelWithDates</v>
       </c>
       <c r="P141" s="8"/>
       <c r="Q141" s="8"/>
       <c r="T141" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -20284,21 +20308,21 @@
       </c>
       <c r="L143" s="2"/>
       <c r="M143" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:string</v>
       </c>
       <c r="N143" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O143" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P143" s="8"/>
       <c r="Q143" s="8"/>
       <c r="T143" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20335,21 +20359,21 @@
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:string</v>
       </c>
       <c r="N144" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O144" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P144" s="8"/>
       <c r="Q144" s="8"/>
       <c r="T144" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20388,15 +20412,15 @@
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>rdf:langString</v>
       </c>
       <c r="N145" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O145" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P145" s="8" t="s">
@@ -20407,7 +20431,7 @@
         <v>271</v>
       </c>
       <c r="T145" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20446,15 +20470,15 @@
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>rdf:langString</v>
       </c>
       <c r="N146" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O146" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P146" s="8"/>
@@ -20463,7 +20487,7 @@
         <v>271</v>
       </c>
       <c r="T146" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20502,21 +20526,21 @@
       </c>
       <c r="L147" s="2"/>
       <c r="M147" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:integer</v>
       </c>
       <c r="N147" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O147" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P147" s="8"/>
       <c r="Q147" s="8"/>
       <c r="T147" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20551,21 +20575,21 @@
       </c>
       <c r="L148" s="2"/>
       <c r="M148" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:string</v>
       </c>
       <c r="N148" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O148" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P148" s="8"/>
       <c r="Q148" s="8"/>
       <c r="T148" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20604,21 +20628,21 @@
       </c>
       <c r="L149" s="2"/>
       <c r="M149" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N149" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:SpecialitePharmaceutique</v>
       </c>
       <c r="O149" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P149" s="8"/>
       <c r="Q149" s="8"/>
       <c r="T149" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20657,70 +20681,70 @@
       </c>
       <c r="L150" s="2"/>
       <c r="M150" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N150" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:UniteCommuneDeDispensation</v>
       </c>
       <c r="O150" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P150" s="8"/>
       <c r="Q150" s="8"/>
       <c r="T150" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
-    <row r="151" ht="63.75">
-      <c r="A151" s="2" t="str">
+    <row r="151" s="39" customFormat="1" ht="63.75">
+      <c r="A151" s="39" t="str">
         <f>CONCATENATE(Préfixes!$B$3,":P",ROW(A151))</f>
         <v>med:P151</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B151" s="39" t="s">
         <v>579</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="C151" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="D151" s="8" t="b">
+      <c r="D151" s="40" t="b">
         <v>1</v>
       </c>
-      <c r="E151" s="8" t="s">
+      <c r="E151" s="40" t="s">
         <v>580</v>
       </c>
-      <c r="F151" s="8" t="s">
+      <c r="F151" s="40" t="s">
         <v>581</v>
       </c>
-      <c r="G151" s="8"/>
-      <c r="H151" s="48">
+      <c r="G151" s="40"/>
+      <c r="H151" s="78">
         <v>2</v>
       </c>
-      <c r="I151" s="49">
+      <c r="I151" s="79">
         <v>2</v>
       </c>
-      <c r="J151" s="2" t="s">
+      <c r="J151" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="M151" s="71" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="N151" s="2" t="str">
+      <c r="M151" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O151" s="2" t="str">
+      <c r="N151" s="39" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="P151" s="8"/>
-      <c r="Q151" s="8"/>
-      <c r="T151" s="8" t="str">
-        <f t="shared" si="13"/>
+      <c r="O151" s="39" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P151" s="40"/>
+      <c r="Q151" s="40"/>
+      <c r="T151" s="40" t="str">
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20755,21 +20779,21 @@
       </c>
       <c r="L152" s="2"/>
       <c r="M152" s="71" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N152" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:PrescriptionEnDC</v>
       </c>
       <c r="O152" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P152" s="8"/>
       <c r="Q152" s="8"/>
       <c r="T152" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -20806,21 +20830,21 @@
       </c>
       <c r="L153" s="2"/>
       <c r="M153" s="71" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>xsd:decimal</v>
       </c>
       <c r="N153" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O153" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P153" s="8"/>
       <c r="Q153" s="8"/>
       <c r="T153" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20857,21 +20881,21 @@
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="71" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>cdt:ucumunit</v>
       </c>
       <c r="N154" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O154" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P154" s="8"/>
       <c r="Q154" s="8"/>
       <c r="T154" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20906,21 +20930,21 @@
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="71" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N155" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:ElementPresentation</v>
       </c>
       <c r="O155" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P155" s="8"/>
       <c r="Q155" s="8"/>
       <c r="T155" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -20955,15 +20979,15 @@
       </c>
       <c r="L156" s="8"/>
       <c r="M156" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N156" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Evenement</v>
       </c>
       <c r="O156" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P156" s="8"/>
@@ -20971,7 +20995,7 @@
       <c r="R156" s="8"/>
       <c r="S156" s="8"/>
       <c r="T156" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U156" s="8"/>
@@ -21017,15 +21041,15 @@
       </c>
       <c r="L157" s="64"/>
       <c r="M157" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N157" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O157" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>med:BlankNode_LabelWithDates</v>
       </c>
       <c r="P157" s="2"/>
@@ -21033,7 +21057,7 @@
       <c r="R157" s="2"/>
       <c r="S157" s="2"/>
       <c r="T157" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="U157" s="2"/>
@@ -21079,15 +21103,15 @@
       </c>
       <c r="L158" s="64"/>
       <c r="M158" s="57" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N158" s="45" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O158" s="45" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>med:BlankNode_LabelWithDates</v>
       </c>
       <c r="P158" s="2"/>
@@ -21095,7 +21119,7 @@
       <c r="R158" s="2"/>
       <c r="S158" s="2"/>
       <c r="T158" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="U158" s="2"/>
@@ -21142,15 +21166,15 @@
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N159" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:DosagePresentation</v>
       </c>
       <c r="O159" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P159" s="8"/>
@@ -21158,7 +21182,7 @@
       <c r="R159" s="2"/>
       <c r="S159" s="2"/>
       <c r="T159" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="U159" s="2"/>
@@ -21205,15 +21229,15 @@
       </c>
       <c r="L160" s="2"/>
       <c r="M160" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N160" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:DosageConcentration</v>
       </c>
       <c r="O160" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P160" s="8"/>
@@ -21221,7 +21245,7 @@
       <c r="R160" s="2"/>
       <c r="S160" s="2"/>
       <c r="T160" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="U160" s="2"/>
@@ -21270,21 +21294,21 @@
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N161" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Voie</v>
       </c>
       <c r="O161" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P161" s="8"/>
       <c r="Q161" s="8"/>
       <c r="T161" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -21323,15 +21347,15 @@
       </c>
       <c r="L162" s="8"/>
       <c r="M162" s="71" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N162" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Forme</v>
       </c>
       <c r="O162" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P162" s="8"/>
@@ -21339,7 +21363,7 @@
       <c r="R162" s="8"/>
       <c r="S162" s="8"/>
       <c r="T162" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="U162" s="8"/>
@@ -21426,15 +21450,15 @@
       </c>
       <c r="L164" s="2"/>
       <c r="M164" s="71" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N164" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>med:Presentation</v>
       </c>
       <c r="O164" s="2" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P164" s="8"/>
@@ -21442,7 +21466,7 @@
       <c r="R164" s="8"/>
       <c r="S164" s="8"/>
       <c r="T164" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U164" s="8"/>
@@ -21458,68 +21482,68 @@
       <c r="AE164" s="8"/>
       <c r="AF164" s="8"/>
     </row>
-    <row r="165" ht="89.25">
-      <c r="A165" s="8" t="str">
+    <row r="165" s="39" customFormat="1" ht="89.25">
+      <c r="A165" s="40" t="str">
         <f>CONCATENATE(Préfixes!$B$3,":P",ROW(A165))</f>
         <v>med:P165</v>
       </c>
-      <c r="B165" s="8" t="s">
+      <c r="B165" s="40" t="s">
         <v>579</v>
       </c>
-      <c r="C165" s="8" t="s">
+      <c r="C165" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="D165" s="8" t="b">
+      <c r="D165" s="40" t="b">
         <v>1</v>
       </c>
-      <c r="E165" s="8" t="s">
+      <c r="E165" s="40" t="s">
         <v>580</v>
       </c>
-      <c r="F165" s="8" t="s">
+      <c r="F165" s="40" t="s">
         <v>604</v>
       </c>
-      <c r="G165" s="8"/>
-      <c r="H165" s="68">
+      <c r="G165" s="40"/>
+      <c r="H165" s="81">
         <v>2</v>
       </c>
-      <c r="I165" s="69">
+      <c r="I165" s="82">
         <v>2</v>
       </c>
-      <c r="J165" s="8" t="s">
+      <c r="J165" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="M165" s="71" t="str">
-        <f t="shared" ref="M165:M228" si="14">IF(K165&lt;&gt;"",IF(OR(LEFT(K165,3)="rdf",LEFT(K165,3)="xsd",LEFT(K165,3)="cdt"),K165,""),"")</f>
-        <v/>
-      </c>
-      <c r="N165" s="2" t="str">
-        <f t="shared" ref="N165:N228" si="15">IF(K165&lt;&gt;"",IF(AND(M165="",LEFT(K165,13)&lt;&gt;"med:BlankNode"),K165,""),"")</f>
-        <v/>
-      </c>
-      <c r="O165" s="2" t="str">
-        <f t="shared" ref="O165:O228" si="16">IF(K165&lt;&gt;"",IF(AND(M165="",LEFT(K165,13)="med:BlankNode"),K165,""),"")</f>
-        <v/>
-      </c>
-      <c r="P165" s="8"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="8" t="str">
-        <f t="shared" si="13"/>
+      <c r="M165" s="80" t="str">
+        <f t="shared" ref="M165:M228" si="15">IF(K165&lt;&gt;"",IF(OR(LEFT(K165,3)="rdf",LEFT(K165,3)="xsd",LEFT(K165,3)="cdt"),K165,""),"")</f>
+        <v/>
+      </c>
+      <c r="N165" s="39" t="str">
+        <f t="shared" ref="N165:N228" si="16">IF(K165&lt;&gt;"",IF(AND(M165="",LEFT(K165,13)&lt;&gt;"med:BlankNode"),K165,""),"")</f>
+        <v/>
+      </c>
+      <c r="O165" s="39" t="str">
+        <f t="shared" ref="O165:O228" si="17">IF(K165&lt;&gt;"",IF(AND(M165="",LEFT(K165,13)="med:BlankNode"),K165,""),"")</f>
+        <v/>
+      </c>
+      <c r="P165" s="40"/>
+      <c r="Q165" s="40"/>
+      <c r="R165" s="40"/>
+      <c r="S165" s="40"/>
+      <c r="T165" s="40" t="str">
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
-      <c r="U165" s="8"/>
-      <c r="V165" s="8"/>
-      <c r="W165" s="8"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="8"/>
-      <c r="Z165" s="8"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="8"/>
-      <c r="AF165" s="8"/>
+      <c r="U165" s="40"/>
+      <c r="V165" s="40"/>
+      <c r="W165" s="40"/>
+      <c r="X165" s="40"/>
+      <c r="Y165" s="40"/>
+      <c r="Z165" s="40"/>
+      <c r="AA165" s="40"/>
+      <c r="AB165" s="40"/>
+      <c r="AC165" s="40"/>
+      <c r="AD165" s="40"/>
+      <c r="AE165" s="40"/>
+      <c r="AF165" s="40"/>
     </row>
     <row r="166" ht="36.75" customHeight="1">
       <c r="A166" s="8" t="str">
@@ -21556,15 +21580,15 @@
       </c>
       <c r="L166" s="8"/>
       <c r="M166" s="71" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N166" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O166" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P166" s="8"/>
@@ -21572,7 +21596,7 @@
       <c r="R166" s="8"/>
       <c r="S166" s="8"/>
       <c r="T166" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U166" s="8"/>
@@ -21623,15 +21647,15 @@
       </c>
       <c r="L167" s="8"/>
       <c r="M167" s="71" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N167" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O167" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P167" s="8" t="s">
@@ -21641,7 +21665,7 @@
       <c r="R167" s="8"/>
       <c r="S167" s="8"/>
       <c r="T167" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U167" s="8"/>
@@ -21692,15 +21716,15 @@
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="71" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N168" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>med:Element</v>
       </c>
       <c r="O168" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P168" s="8"/>
@@ -21708,7 +21732,7 @@
       <c r="R168" s="8"/>
       <c r="S168" s="8"/>
       <c r="T168" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U168" s="8"/>
@@ -21759,15 +21783,15 @@
       </c>
       <c r="L169" s="2"/>
       <c r="M169" s="71" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N169" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O169" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P169" s="8"/>
@@ -21775,7 +21799,7 @@
       <c r="R169" s="8"/>
       <c r="S169" s="8"/>
       <c r="T169" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U169" s="8"/>
@@ -21826,15 +21850,15 @@
       </c>
       <c r="L170" s="2"/>
       <c r="M170" s="71" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N170" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>med:TypeContenant</v>
       </c>
       <c r="O170" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P170" s="8"/>
@@ -21842,7 +21866,7 @@
       <c r="R170" s="8"/>
       <c r="S170" s="8"/>
       <c r="T170" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="U170" s="8"/>
@@ -21889,15 +21913,15 @@
       </c>
       <c r="L171" s="2"/>
       <c r="M171" s="71" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N171" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>med:PPhParSubstanceDosageForme</v>
       </c>
       <c r="O171" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P171" s="8"/>
@@ -21905,7 +21929,7 @@
       <c r="R171" s="8"/>
       <c r="S171" s="8"/>
       <c r="T171" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="U171" s="8"/>
@@ -21954,15 +21978,15 @@
       </c>
       <c r="L172" s="2"/>
       <c r="M172" s="71" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N172" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>med:PPhParSubstance</v>
       </c>
       <c r="O172" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P172" s="8"/>
@@ -21970,7 +21994,7 @@
       <c r="R172" s="8"/>
       <c r="S172" s="8"/>
       <c r="T172" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="U172" s="8"/>
@@ -22017,15 +22041,15 @@
       </c>
       <c r="L173" s="2"/>
       <c r="M173" s="2" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N173" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>med:Forme</v>
       </c>
       <c r="O173" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P173" s="8"/>
@@ -22033,7 +22057,7 @@
       <c r="R173" s="8"/>
       <c r="S173" s="8"/>
       <c r="T173" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="U173" s="8"/>
@@ -22082,15 +22106,15 @@
       </c>
       <c r="L174" s="2"/>
       <c r="M174" s="71" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N174" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>med:DosagePresentation</v>
       </c>
       <c r="O174" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P174" s="8"/>
@@ -22098,7 +22122,7 @@
       <c r="R174" s="8"/>
       <c r="S174" s="8"/>
       <c r="T174" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="U174" s="8"/>
@@ -22145,15 +22169,15 @@
       </c>
       <c r="L175" s="64"/>
       <c r="M175" s="2" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N175" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>med:UniteDePresentation</v>
       </c>
       <c r="O175" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P175" s="8"/>
@@ -22161,7 +22185,7 @@
       <c r="R175" s="8"/>
       <c r="S175" s="8"/>
       <c r="T175" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="U175" s="8"/>
@@ -22210,15 +22234,15 @@
       </c>
       <c r="L176" s="64"/>
       <c r="M176" s="2" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N176" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>med:TypeDose</v>
       </c>
       <c r="O176" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P176" s="8"/>
@@ -22226,7 +22250,7 @@
       <c r="R176" s="8"/>
       <c r="S176" s="8"/>
       <c r="T176" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="U176" s="8"/>
@@ -22249,11 +22273,11 @@
       </c>
       <c r="C177" s="24"/>
       <c r="D177" s="24"/>
-      <c r="E177" s="78"/>
-      <c r="F177" s="78"/>
+      <c r="E177" s="83"/>
+      <c r="F177" s="83"/>
       <c r="G177" s="24"/>
-      <c r="H177" s="79"/>
-      <c r="I177" s="80"/>
+      <c r="H177" s="84"/>
+      <c r="I177" s="85"/>
       <c r="J177" s="24"/>
       <c r="K177" s="24"/>
       <c r="L177" s="24"/>
@@ -22313,7 +22337,7 @@
       </c>
       <c r="L178" s="2"/>
       <c r="M178" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N178" s="45"/>
@@ -22323,7 +22347,7 @@
       <c r="R178" s="2"/>
       <c r="S178" s="2"/>
       <c r="T178" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U178" s="2"/>
@@ -22374,7 +22398,7 @@
       </c>
       <c r="L179" s="2"/>
       <c r="M179" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N179" s="45"/>
@@ -22386,7 +22410,7 @@
       <c r="R179" s="2"/>
       <c r="S179" s="2"/>
       <c r="T179" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U179" s="2"/>
@@ -22437,7 +22461,7 @@
       </c>
       <c r="L180" s="2"/>
       <c r="M180" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N180" s="45"/>
@@ -22447,7 +22471,7 @@
       <c r="R180" s="2"/>
       <c r="S180" s="2"/>
       <c r="T180" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
       <c r="U180" s="2"/>
@@ -22473,8 +22497,8 @@
       <c r="E181" s="24"/>
       <c r="F181" s="24"/>
       <c r="G181" s="24"/>
-      <c r="H181" s="79"/>
-      <c r="I181" s="80"/>
+      <c r="H181" s="84"/>
+      <c r="I181" s="85"/>
       <c r="J181" s="24"/>
       <c r="K181" s="24"/>
       <c r="L181" s="24"/>
@@ -22534,7 +22558,7 @@
       </c>
       <c r="L182" s="2"/>
       <c r="M182" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N182" s="45"/>
@@ -22543,7 +22567,7 @@
       <c r="Q182" s="8"/>
       <c r="R182" s="2"/>
       <c r="T182" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -22582,14 +22606,14 @@
       </c>
       <c r="L183" s="2"/>
       <c r="M183" s="71" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:date</v>
       </c>
       <c r="P183" s="8"/>
       <c r="Q183" s="8"/>
       <c r="R183" s="2"/>
       <c r="T183" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -22626,7 +22650,7 @@
       </c>
       <c r="L184" s="2"/>
       <c r="M184" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N184" s="45"/>
@@ -22635,7 +22659,7 @@
       <c r="Q184" s="8"/>
       <c r="R184" s="2"/>
       <c r="T184" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -22672,15 +22696,15 @@
       </c>
       <c r="L185" s="2"/>
       <c r="M185" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N185" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O185" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P185" s="8" t="s">
@@ -22691,7 +22715,7 @@
         <v>271</v>
       </c>
       <c r="T185" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -22726,15 +22750,15 @@
       </c>
       <c r="L186" s="2"/>
       <c r="M186" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N186" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O186" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P186" s="8"/>
@@ -22743,7 +22767,7 @@
         <v>271</v>
       </c>
       <c r="T186" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -22778,21 +22802,21 @@
       </c>
       <c r="L187" s="2"/>
       <c r="M187" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N187" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>med:SpecialitePharmaceutique</v>
       </c>
       <c r="O187" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P187" s="8"/>
       <c r="Q187" s="8"/>
       <c r="T187" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -22827,21 +22851,21 @@
       </c>
       <c r="L188" s="2"/>
       <c r="M188" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N188" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>med:SpecialitePharmaceutique</v>
       </c>
       <c r="O188" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P188" s="8"/>
       <c r="Q188" s="8"/>
       <c r="T188" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -22874,21 +22898,21 @@
       <c r="K189" s="2"/>
       <c r="L189" s="2"/>
       <c r="M189" s="71" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N189" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O189" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P189" s="8"/>
       <c r="Q189" s="8"/>
       <c r="T189" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -22902,8 +22926,8 @@
       <c r="E190" s="24"/>
       <c r="F190" s="24"/>
       <c r="G190" s="24"/>
-      <c r="H190" s="79"/>
-      <c r="I190" s="80"/>
+      <c r="H190" s="84"/>
+      <c r="I190" s="85"/>
       <c r="J190" s="24"/>
       <c r="K190" s="24"/>
       <c r="L190" s="24"/>
@@ -22963,7 +22987,7 @@
       </c>
       <c r="L191" s="2"/>
       <c r="M191" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N191" s="45"/>
@@ -22972,7 +22996,7 @@
       <c r="Q191" s="8"/>
       <c r="R191" s="2"/>
       <c r="T191" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -23009,15 +23033,15 @@
       </c>
       <c r="L192" s="2"/>
       <c r="M192" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N192" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O192" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P192" s="8" t="s">
@@ -23028,7 +23052,7 @@
         <v>271</v>
       </c>
       <c r="T192" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -23065,22 +23089,22 @@
       </c>
       <c r="L193" s="2"/>
       <c r="M193" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N193" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O193" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P193" s="8"/>
       <c r="Q193" s="8"/>
       <c r="R193" s="2"/>
       <c r="T193" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -23117,22 +23141,22 @@
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N194" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O194" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P194" s="8"/>
       <c r="Q194" s="8"/>
       <c r="R194" s="2"/>
       <c r="T194" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -23165,22 +23189,22 @@
       <c r="K195" s="2"/>
       <c r="L195" s="2"/>
       <c r="M195" s="71" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N195" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O195" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P195" s="8"/>
       <c r="Q195" s="8"/>
       <c r="R195" s="2"/>
       <c r="T195" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -23194,8 +23218,8 @@
       <c r="E196" s="24"/>
       <c r="F196" s="24"/>
       <c r="G196" s="24"/>
-      <c r="H196" s="79"/>
-      <c r="I196" s="80"/>
+      <c r="H196" s="84"/>
+      <c r="I196" s="85"/>
       <c r="J196" s="24"/>
       <c r="K196" s="24"/>
       <c r="L196" s="24"/>
@@ -23253,7 +23277,7 @@
       </c>
       <c r="L197" s="2"/>
       <c r="M197" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N197" s="45"/>
@@ -23262,7 +23286,7 @@
       <c r="Q197" s="8"/>
       <c r="R197" s="2"/>
       <c r="T197" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -23297,15 +23321,15 @@
       </c>
       <c r="L198" s="2"/>
       <c r="M198" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N198" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O198" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P198" s="8" t="s">
@@ -23316,7 +23340,7 @@
         <v>271</v>
       </c>
       <c r="T198" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -23347,22 +23371,22 @@
       <c r="K199" s="2"/>
       <c r="L199" s="2"/>
       <c r="M199" s="71" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N199" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O199" s="2" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P199" s="8"/>
       <c r="Q199" s="8"/>
       <c r="R199" s="2"/>
       <c r="T199" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -23376,8 +23400,8 @@
       <c r="E200" s="24"/>
       <c r="F200" s="24"/>
       <c r="G200" s="24"/>
-      <c r="H200" s="79"/>
-      <c r="I200" s="80"/>
+      <c r="H200" s="84"/>
+      <c r="I200" s="85"/>
       <c r="J200" s="24"/>
       <c r="K200" s="24"/>
       <c r="L200" s="24"/>
@@ -23437,7 +23461,7 @@
       </c>
       <c r="L201" s="2"/>
       <c r="M201" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N201" s="45"/>
@@ -23446,7 +23470,7 @@
       <c r="Q201" s="8"/>
       <c r="R201" s="2"/>
       <c r="T201" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -23483,15 +23507,15 @@
       </c>
       <c r="L202" s="2"/>
       <c r="M202" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N202" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O202" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P202" s="8" t="s">
@@ -23502,45 +23526,45 @@
         <v>271</v>
       </c>
       <c r="T202" s="8" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="203" ht="18">
-      <c r="A203" s="78"/>
-      <c r="B203" s="78" t="s">
+      <c r="A203" s="83"/>
+      <c r="B203" s="83" t="s">
         <v>667</v>
       </c>
-      <c r="C203" s="78"/>
-      <c r="D203" s="78"/>
-      <c r="E203" s="78"/>
-      <c r="F203" s="78"/>
-      <c r="G203" s="78"/>
-      <c r="H203" s="81"/>
-      <c r="I203" s="82"/>
-      <c r="J203" s="78"/>
-      <c r="K203" s="78"/>
-      <c r="L203" s="78"/>
-      <c r="M203" s="78"/>
-      <c r="N203" s="78"/>
-      <c r="O203" s="78"/>
-      <c r="P203" s="78"/>
-      <c r="Q203" s="78"/>
-      <c r="R203" s="78"/>
-      <c r="S203" s="78"/>
-      <c r="T203" s="78"/>
-      <c r="U203" s="78"/>
-      <c r="V203" s="78"/>
-      <c r="W203" s="78"/>
-      <c r="X203" s="78"/>
-      <c r="Y203" s="78"/>
-      <c r="Z203" s="78"/>
-      <c r="AA203" s="78"/>
-      <c r="AB203" s="78"/>
-      <c r="AC203" s="78"/>
-      <c r="AD203" s="78"/>
-      <c r="AE203" s="78"/>
-      <c r="AF203" s="78"/>
+      <c r="C203" s="83"/>
+      <c r="D203" s="83"/>
+      <c r="E203" s="83"/>
+      <c r="F203" s="83"/>
+      <c r="G203" s="83"/>
+      <c r="H203" s="86"/>
+      <c r="I203" s="87"/>
+      <c r="J203" s="83"/>
+      <c r="K203" s="83"/>
+      <c r="L203" s="83"/>
+      <c r="M203" s="83"/>
+      <c r="N203" s="83"/>
+      <c r="O203" s="83"/>
+      <c r="P203" s="83"/>
+      <c r="Q203" s="83"/>
+      <c r="R203" s="83"/>
+      <c r="S203" s="83"/>
+      <c r="T203" s="83"/>
+      <c r="U203" s="83"/>
+      <c r="V203" s="83"/>
+      <c r="W203" s="83"/>
+      <c r="X203" s="83"/>
+      <c r="Y203" s="83"/>
+      <c r="Z203" s="83"/>
+      <c r="AA203" s="83"/>
+      <c r="AB203" s="83"/>
+      <c r="AC203" s="83"/>
+      <c r="AD203" s="83"/>
+      <c r="AE203" s="83"/>
+      <c r="AF203" s="83"/>
     </row>
     <row r="204" ht="25.5">
       <c r="A204" s="2" t="str">
@@ -23575,7 +23599,7 @@
       </c>
       <c r="L204" s="2"/>
       <c r="M204" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N204" s="45"/>
@@ -23584,7 +23608,7 @@
       <c r="Q204" s="8"/>
       <c r="R204" s="2"/>
       <c r="T204" s="8" t="str">
-        <f t="shared" ref="T203:T254" si="17">IF(D204=TRUE,"#EAF1DD","")</f>
+        <f t="shared" ref="T203:T254" si="18">IF(D204=TRUE,"#EAF1DD","")</f>
         <v/>
       </c>
     </row>
@@ -23619,15 +23643,15 @@
       </c>
       <c r="L205" s="2"/>
       <c r="M205" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N205" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O205" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P205" s="8" t="s">
@@ -23638,45 +23662,45 @@
         <v>271</v>
       </c>
       <c r="T205" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="206" ht="18">
-      <c r="A206" s="78"/>
-      <c r="B206" s="78" t="s">
+      <c r="A206" s="83"/>
+      <c r="B206" s="83" t="s">
         <v>155</v>
       </c>
-      <c r="C206" s="78"/>
-      <c r="D206" s="78"/>
-      <c r="E206" s="78"/>
-      <c r="F206" s="78"/>
-      <c r="G206" s="78"/>
-      <c r="H206" s="81"/>
-      <c r="I206" s="82"/>
-      <c r="J206" s="78"/>
-      <c r="K206" s="78"/>
-      <c r="L206" s="78"/>
-      <c r="M206" s="78"/>
-      <c r="N206" s="78"/>
-      <c r="O206" s="78"/>
-      <c r="P206" s="78"/>
-      <c r="Q206" s="78"/>
-      <c r="R206" s="78"/>
-      <c r="S206" s="78"/>
-      <c r="T206" s="78"/>
-      <c r="U206" s="78"/>
-      <c r="V206" s="78"/>
-      <c r="W206" s="78"/>
-      <c r="X206" s="78"/>
-      <c r="Y206" s="78"/>
-      <c r="Z206" s="78"/>
-      <c r="AA206" s="78"/>
-      <c r="AB206" s="78"/>
-      <c r="AC206" s="78"/>
-      <c r="AD206" s="78"/>
-      <c r="AE206" s="78"/>
-      <c r="AF206" s="78"/>
+      <c r="C206" s="83"/>
+      <c r="D206" s="83"/>
+      <c r="E206" s="83"/>
+      <c r="F206" s="83"/>
+      <c r="G206" s="83"/>
+      <c r="H206" s="86"/>
+      <c r="I206" s="87"/>
+      <c r="J206" s="83"/>
+      <c r="K206" s="83"/>
+      <c r="L206" s="83"/>
+      <c r="M206" s="83"/>
+      <c r="N206" s="83"/>
+      <c r="O206" s="83"/>
+      <c r="P206" s="83"/>
+      <c r="Q206" s="83"/>
+      <c r="R206" s="83"/>
+      <c r="S206" s="83"/>
+      <c r="T206" s="83"/>
+      <c r="U206" s="83"/>
+      <c r="V206" s="83"/>
+      <c r="W206" s="83"/>
+      <c r="X206" s="83"/>
+      <c r="Y206" s="83"/>
+      <c r="Z206" s="83"/>
+      <c r="AA206" s="83"/>
+      <c r="AB206" s="83"/>
+      <c r="AC206" s="83"/>
+      <c r="AD206" s="83"/>
+      <c r="AE206" s="83"/>
+      <c r="AF206" s="83"/>
     </row>
     <row r="207" ht="12.75">
       <c r="A207" s="2" t="str">
@@ -23713,7 +23737,7 @@
       </c>
       <c r="L207" s="2"/>
       <c r="M207" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N207" s="45"/>
@@ -23722,7 +23746,7 @@
       <c r="Q207" s="8"/>
       <c r="R207" s="2"/>
       <c r="T207" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -23761,15 +23785,15 @@
       </c>
       <c r="L208" s="2"/>
       <c r="M208" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N208" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O208" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P208" s="8" t="s">
@@ -23780,7 +23804,7 @@
         <v>271</v>
       </c>
       <c r="T208" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -23817,22 +23841,22 @@
       </c>
       <c r="L209" s="2"/>
       <c r="M209" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N209" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>med:SpecialitePharmaceutique</v>
       </c>
       <c r="O209" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P209" s="8"/>
       <c r="Q209" s="8"/>
       <c r="R209" s="2"/>
       <c r="T209" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -23846,8 +23870,8 @@
       <c r="E210" s="24"/>
       <c r="F210" s="24"/>
       <c r="G210" s="24"/>
-      <c r="H210" s="79"/>
-      <c r="I210" s="80"/>
+      <c r="H210" s="84"/>
+      <c r="I210" s="85"/>
       <c r="J210" s="24"/>
       <c r="K210" s="24"/>
       <c r="L210" s="24"/>
@@ -23905,15 +23929,15 @@
       </c>
       <c r="L211" s="2"/>
       <c r="M211" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N211" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O211" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P211" s="8" t="s">
@@ -23924,7 +23948,7 @@
         <v>271</v>
       </c>
       <c r="T211" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -23959,15 +23983,15 @@
       </c>
       <c r="L212" s="2"/>
       <c r="M212" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N212" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O212" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P212" s="8"/>
@@ -23976,7 +24000,7 @@
         <v>271</v>
       </c>
       <c r="T212" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -23990,8 +24014,8 @@
       <c r="E213" s="24"/>
       <c r="F213" s="24"/>
       <c r="G213" s="24"/>
-      <c r="H213" s="79"/>
-      <c r="I213" s="80"/>
+      <c r="H213" s="84"/>
+      <c r="I213" s="85"/>
       <c r="J213" s="24"/>
       <c r="K213" s="24"/>
       <c r="L213" s="24"/>
@@ -24049,15 +24073,15 @@
       </c>
       <c r="L214" s="2"/>
       <c r="M214" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N214" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O214" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P214" s="8" t="s">
@@ -24068,7 +24092,7 @@
         <v>271</v>
       </c>
       <c r="T214" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -24082,8 +24106,8 @@
       <c r="E215" s="35"/>
       <c r="F215" s="35"/>
       <c r="G215" s="35"/>
-      <c r="H215" s="83"/>
-      <c r="I215" s="84"/>
+      <c r="H215" s="88"/>
+      <c r="I215" s="89"/>
       <c r="J215" s="35"/>
       <c r="K215" s="35"/>
       <c r="L215" s="35"/>
@@ -24143,15 +24167,15 @@
       </c>
       <c r="L216" s="2"/>
       <c r="M216" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N216" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O216" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P216" s="8" t="s">
@@ -24162,7 +24186,7 @@
         <v>271</v>
       </c>
       <c r="T216" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -24199,21 +24223,21 @@
       </c>
       <c r="L217" s="2"/>
       <c r="M217" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:date</v>
       </c>
       <c r="N217" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O217" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P217" s="8"/>
       <c r="Q217" s="8"/>
       <c r="T217" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -24252,21 +24276,21 @@
       </c>
       <c r="L218" s="2"/>
       <c r="M218" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:date</v>
       </c>
       <c r="N218" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O218" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P218" s="8"/>
       <c r="Q218" s="8"/>
       <c r="T218" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -24303,21 +24327,21 @@
       </c>
       <c r="L219" s="2"/>
       <c r="M219" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N219" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O219" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P219" s="8"/>
       <c r="Q219" s="8"/>
       <c r="T219" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -24355,16 +24379,16 @@
       </c>
       <c r="K220" s="2"/>
       <c r="L220" s="2"/>
-      <c r="M220" s="85"/>
+      <c r="M220" s="90"/>
       <c r="N220" s="45"/>
       <c r="O220" s="45"/>
       <c r="P220" s="8"/>
       <c r="Q220" s="8"/>
-      <c r="S220" s="8" t="s">
+      <c r="S220" s="91" t="s">
         <v>694</v>
       </c>
       <c r="T220" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -24403,21 +24427,21 @@
       </c>
       <c r="L221" s="2"/>
       <c r="M221" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N221" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>med:TypeEvenement</v>
       </c>
       <c r="O221" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P221" s="8"/>
       <c r="Q221" s="8"/>
       <c r="T221" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -24431,8 +24455,8 @@
       <c r="E222" s="35"/>
       <c r="F222" s="35"/>
       <c r="G222" s="35"/>
-      <c r="H222" s="83"/>
-      <c r="I222" s="84"/>
+      <c r="H222" s="88"/>
+      <c r="I222" s="89"/>
       <c r="J222" s="35"/>
       <c r="K222" s="35"/>
       <c r="L222" s="35"/>
@@ -24490,21 +24514,21 @@
       </c>
       <c r="L223" s="2"/>
       <c r="M223" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N223" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>med:TypeProcedure</v>
       </c>
       <c r="O223" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P223" s="8"/>
       <c r="Q223" s="8"/>
       <c r="T223" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -24518,8 +24542,8 @@
       <c r="E224" s="24"/>
       <c r="F224" s="24"/>
       <c r="G224" s="24"/>
-      <c r="H224" s="79"/>
-      <c r="I224" s="80"/>
+      <c r="H224" s="84"/>
+      <c r="I224" s="85"/>
       <c r="J224" s="24"/>
       <c r="K224" s="24"/>
       <c r="L224" s="24"/>
@@ -24579,15 +24603,15 @@
       </c>
       <c r="L225" s="2"/>
       <c r="M225" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N225" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O225" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P225" s="8" t="s">
@@ -24598,7 +24622,7 @@
         <v>271</v>
       </c>
       <c r="T225" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -24635,15 +24659,15 @@
       </c>
       <c r="L226" s="2"/>
       <c r="M226" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>rdf:langString</v>
       </c>
       <c r="N226" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O226" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P226" s="8"/>
@@ -24652,7 +24676,7 @@
         <v>271</v>
       </c>
       <c r="T226" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -24691,21 +24715,21 @@
       </c>
       <c r="L227" s="2"/>
       <c r="M227" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:string</v>
       </c>
       <c r="N227" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O227" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P227" s="8"/>
       <c r="Q227" s="8"/>
       <c r="T227" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -24742,21 +24766,21 @@
       </c>
       <c r="L228" s="2"/>
       <c r="M228" s="57" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>xsd:date</v>
       </c>
       <c r="N228" s="45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O228" s="45" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P228" s="8"/>
       <c r="Q228" s="8"/>
       <c r="T228" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -24793,21 +24817,21 @@
       </c>
       <c r="L229" s="2"/>
       <c r="M229" s="57" t="str">
-        <f t="shared" ref="M229:M254" si="18">IF(K229&lt;&gt;"",IF(OR(LEFT(K229,3)="rdf",LEFT(K229,3)="xsd",LEFT(K229,3)="cdt"),K229,""),"")</f>
+        <f t="shared" ref="M229:M254" si="19">IF(K229&lt;&gt;"",IF(OR(LEFT(K229,3)="rdf",LEFT(K229,3)="xsd",LEFT(K229,3)="cdt"),K229,""),"")</f>
         <v>xsd:date</v>
       </c>
       <c r="N229" s="45" t="str">
-        <f t="shared" ref="N229:N254" si="19">IF(K229&lt;&gt;"",IF(AND(M229="",LEFT(K229,13)&lt;&gt;"med:BlankNode"),K229,""),"")</f>
+        <f t="shared" ref="N229:N254" si="20">IF(K229&lt;&gt;"",IF(AND(M229="",LEFT(K229,13)&lt;&gt;"med:BlankNode"),K229,""),"")</f>
         <v/>
       </c>
       <c r="O229" s="45" t="str">
-        <f t="shared" ref="O229:O254" si="20">IF(K229&lt;&gt;"",IF(AND(M229="",LEFT(K229,13)="med:BlankNode"),K229,""),"")</f>
+        <f t="shared" ref="O229:O254" si="21">IF(K229&lt;&gt;"",IF(AND(M229="",LEFT(K229,13)="med:BlankNode"),K229,""),"")</f>
         <v/>
       </c>
       <c r="P229" s="8"/>
       <c r="Q229" s="8"/>
       <c r="T229" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -24844,21 +24868,21 @@
       </c>
       <c r="L230" s="2"/>
       <c r="M230" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>xsd:boolean</v>
       </c>
       <c r="N230" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O230" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P230" s="8"/>
       <c r="Q230" s="8"/>
       <c r="T230" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -24872,8 +24896,8 @@
       <c r="E231" s="24"/>
       <c r="F231" s="24"/>
       <c r="G231" s="24"/>
-      <c r="H231" s="79"/>
-      <c r="I231" s="80"/>
+      <c r="H231" s="84"/>
+      <c r="I231" s="85"/>
       <c r="J231" s="24"/>
       <c r="K231" s="24"/>
       <c r="L231" s="24"/>
@@ -24933,15 +24957,15 @@
       </c>
       <c r="L232" s="2"/>
       <c r="M232" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>rdf:langString</v>
       </c>
       <c r="N232" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O232" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P232" s="8" t="s">
@@ -24952,7 +24976,7 @@
         <v>271</v>
       </c>
       <c r="T232" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -24989,15 +25013,15 @@
       </c>
       <c r="L233" s="2"/>
       <c r="M233" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>rdf:langString</v>
       </c>
       <c r="N233" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O233" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P233" s="8"/>
@@ -25006,7 +25030,7 @@
         <v>271</v>
       </c>
       <c r="T233" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -25045,21 +25069,21 @@
       </c>
       <c r="L234" s="2"/>
       <c r="M234" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>xsd:string</v>
       </c>
       <c r="N234" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O234" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P234" s="8"/>
       <c r="Q234" s="8"/>
       <c r="T234" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -25096,21 +25120,21 @@
       </c>
       <c r="L235" s="2"/>
       <c r="M235" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>xsd:date</v>
       </c>
       <c r="N235" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O235" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P235" s="8"/>
       <c r="Q235" s="8"/>
       <c r="T235" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -25147,21 +25171,21 @@
       </c>
       <c r="L236" s="2"/>
       <c r="M236" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>xsd:date</v>
       </c>
       <c r="N236" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O236" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P236" s="8"/>
       <c r="Q236" s="8"/>
       <c r="T236" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -25198,21 +25222,21 @@
       </c>
       <c r="L237" s="2"/>
       <c r="M237" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>xsd:boolean</v>
       </c>
       <c r="N237" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O237" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P237" s="8"/>
       <c r="Q237" s="8"/>
       <c r="T237" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -25226,8 +25250,8 @@
       <c r="E238" s="24"/>
       <c r="F238" s="24"/>
       <c r="G238" s="24"/>
-      <c r="H238" s="79"/>
-      <c r="I238" s="80"/>
+      <c r="H238" s="84"/>
+      <c r="I238" s="85"/>
       <c r="J238" s="24"/>
       <c r="K238" s="24"/>
       <c r="L238" s="24"/>
@@ -25287,15 +25311,15 @@
       </c>
       <c r="L239" s="2"/>
       <c r="M239" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>rdf:langString</v>
       </c>
       <c r="N239" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O239" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P239" s="8" t="s">
@@ -25306,7 +25330,7 @@
         <v>271</v>
       </c>
       <c r="T239" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -25343,15 +25367,15 @@
       </c>
       <c r="L240" s="2"/>
       <c r="M240" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>rdf:langString</v>
       </c>
       <c r="N240" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O240" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P240" s="8"/>
@@ -25360,7 +25384,7 @@
         <v>271</v>
       </c>
       <c r="T240" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -25399,21 +25423,21 @@
       </c>
       <c r="L241" s="2"/>
       <c r="M241" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>xsd:string</v>
       </c>
       <c r="N241" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O241" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P241" s="8"/>
       <c r="Q241" s="8"/>
       <c r="T241" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -25450,21 +25474,21 @@
       </c>
       <c r="L242" s="2"/>
       <c r="M242" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>xsd:date</v>
       </c>
       <c r="N242" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O242" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P242" s="8"/>
       <c r="Q242" s="8"/>
       <c r="T242" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -25501,21 +25525,21 @@
       </c>
       <c r="L243" s="2"/>
       <c r="M243" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>xsd:date</v>
       </c>
       <c r="N243" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O243" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P243" s="8"/>
       <c r="Q243" s="8"/>
       <c r="T243" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
@@ -25552,27 +25576,27 @@
       </c>
       <c r="L244" s="2"/>
       <c r="M244" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>xsd:boolean</v>
       </c>
       <c r="N244" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O244" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P244" s="8"/>
       <c r="Q244" s="8"/>
       <c r="T244" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>#EAF1DD</v>
       </c>
     </row>
     <row r="245" ht="18">
       <c r="A245" s="24"/>
-      <c r="B245" s="86" t="s">
+      <c r="B245" s="92" t="s">
         <v>718</v>
       </c>
       <c r="C245" s="24"/>
@@ -25580,8 +25604,8 @@
       <c r="E245" s="24"/>
       <c r="F245" s="24"/>
       <c r="G245" s="24"/>
-      <c r="H245" s="79"/>
-      <c r="I245" s="80"/>
+      <c r="H245" s="84"/>
+      <c r="I245" s="85"/>
       <c r="J245" s="24"/>
       <c r="K245" s="24"/>
       <c r="L245" s="24"/>
@@ -25637,15 +25661,15 @@
       </c>
       <c r="L246" s="2"/>
       <c r="M246" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>rdf:langString</v>
       </c>
       <c r="N246" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O246" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P246" s="8" t="s">
@@ -25656,7 +25680,7 @@
         <v>271</v>
       </c>
       <c r="T246" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -25693,47 +25717,47 @@
       </c>
       <c r="L247" s="2"/>
       <c r="M247" s="71" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>xsd:string</v>
       </c>
       <c r="N247" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O247" s="2" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P247" s="8"/>
       <c r="Q247" s="8"/>
       <c r="T247" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="248" ht="18">
       <c r="A248" s="24"/>
-      <c r="B248" s="86" t="s">
+      <c r="B248" s="92" t="s">
         <v>719</v>
       </c>
       <c r="C248" s="24"/>
       <c r="D248" s="24"/>
-      <c r="E248" s="78"/>
-      <c r="F248" s="78"/>
-      <c r="G248" s="78"/>
-      <c r="H248" s="79"/>
-      <c r="I248" s="80"/>
+      <c r="E248" s="83"/>
+      <c r="F248" s="83"/>
+      <c r="G248" s="83"/>
+      <c r="H248" s="84"/>
+      <c r="I248" s="85"/>
       <c r="J248" s="24"/>
       <c r="K248" s="24"/>
       <c r="L248" s="24"/>
       <c r="M248" s="24"/>
       <c r="N248" s="24"/>
       <c r="O248" s="24"/>
-      <c r="P248" s="78"/>
-      <c r="Q248" s="78"/>
+      <c r="P248" s="83"/>
+      <c r="Q248" s="83"/>
       <c r="R248" s="24"/>
       <c r="S248" s="24"/>
-      <c r="T248" s="78"/>
+      <c r="T248" s="83"/>
       <c r="U248" s="24"/>
       <c r="V248" s="24"/>
       <c r="W248" s="24"/>
@@ -25778,15 +25802,15 @@
       </c>
       <c r="L249" s="2"/>
       <c r="M249" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>rdf:langString</v>
       </c>
       <c r="N249" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O249" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P249" s="8" t="s">
@@ -25797,7 +25821,7 @@
         <v>271</v>
       </c>
       <c r="T249" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="U249" s="24"/>
@@ -25846,21 +25870,21 @@
       </c>
       <c r="L250" s="2"/>
       <c r="M250" s="71" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>xsd:string</v>
       </c>
       <c r="N250" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O250" s="2" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P250" s="8"/>
       <c r="Q250" s="8"/>
       <c r="T250" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -25871,11 +25895,11 @@
       </c>
       <c r="C251" s="43"/>
       <c r="D251" s="43"/>
-      <c r="E251" s="87"/>
-      <c r="F251" s="87"/>
-      <c r="G251" s="87"/>
-      <c r="H251" s="88"/>
-      <c r="I251" s="89"/>
+      <c r="E251" s="93"/>
+      <c r="F251" s="93"/>
+      <c r="G251" s="93"/>
+      <c r="H251" s="94"/>
+      <c r="I251" s="95"/>
       <c r="J251" s="43"/>
       <c r="K251" s="43"/>
       <c r="L251" s="43"/>
@@ -25933,21 +25957,21 @@
       </c>
       <c r="L252" s="2"/>
       <c r="M252" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>xsd:date</v>
       </c>
       <c r="N252" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O252" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P252" s="8"/>
       <c r="Q252" s="8"/>
       <c r="T252" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -25982,21 +26006,21 @@
       </c>
       <c r="L253" s="2"/>
       <c r="M253" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>xsd:date</v>
       </c>
       <c r="N253" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O253" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P253" s="8"/>
       <c r="Q253" s="8"/>
       <c r="T253" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -26033,21 +26057,21 @@
       </c>
       <c r="L254" s="2"/>
       <c r="M254" s="57" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>rdf:langString</v>
       </c>
       <c r="N254" s="45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O254" s="45" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P254" s="8"/>
       <c r="Q254" s="8"/>
       <c r="T254" s="8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -37320,7 +37344,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75">
-      <c r="A1" s="90" t="str">
+      <c r="A1" s="96" t="str">
         <f>Classes!A1</f>
         <v xml:space="preserve">URI de l'ontologie</v>
       </c>
@@ -37372,7 +37396,7 @@
     </row>
     <row r="8" ht="102">
       <c r="A8" s="2" t="str">
-        <f t="shared" ref="A8:A16" si="21">CONCATENATE("med:BusinessRule_",ROW(A8)-7)</f>
+        <f t="shared" ref="A8:A16" si="22">CONCATENATE("med:BusinessRule_",ROW(A8)-7)</f>
         <v>med:BusinessRule_1</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -37393,7 +37417,7 @@
     </row>
     <row r="9" ht="102">
       <c r="A9" s="2" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>med:BusinessRule_2</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -37414,7 +37438,7 @@
     </row>
     <row r="10" ht="140.25">
       <c r="A10" s="2" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>med:BusinessRule_3</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -37429,13 +37453,13 @@
       <c r="E10" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="91" t="s">
         <v>738</v>
       </c>
     </row>
     <row r="11" ht="140.25">
       <c r="A11" s="2" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>med:BusinessRule_4</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -37450,13 +37474,13 @@
       <c r="E11" s="8" t="s">
         <v>740</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="91" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="12" ht="127.5">
       <c r="A12" s="2" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>med:BusinessRule_5</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -37471,13 +37495,13 @@
       <c r="E12" s="8" t="s">
         <v>743</v>
       </c>
-      <c r="F12" s="91" t="s">
+      <c r="F12" s="97" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="13" ht="127.5">
       <c r="A13" s="2" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>med:BusinessRule_6</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -37492,13 +37516,13 @@
       <c r="E13" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="F13" s="91" t="s">
+      <c r="F13" s="97" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="14" ht="127.5">
       <c r="A14" s="2" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>med:BusinessRule_7</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -37513,13 +37537,13 @@
       <c r="E14" s="8" t="s">
         <v>749</v>
       </c>
-      <c r="F14" s="91" t="s">
+      <c r="F14" s="97" t="s">
         <v>750</v>
       </c>
     </row>
     <row r="15" ht="127.5">
       <c r="A15" s="2" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>med:BusinessRule_8</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -37534,13 +37558,13 @@
       <c r="E15" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="F15" s="91" t="s">
+      <c r="F15" s="97" t="s">
         <v>753</v>
       </c>
     </row>
     <row r="16" ht="102">
       <c r="A16" s="2" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>med:BusinessRule_9</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -37561,7 +37585,7 @@
     </row>
     <row r="17" ht="127.5">
       <c r="A17" s="2" t="str">
-        <f t="shared" ref="A17:A23" si="22">CONCATENATE("med:BusinessRule_",ROW(A17)-7)</f>
+        <f t="shared" ref="A17:A23" si="23">CONCATENATE("med:BusinessRule_",ROW(A17)-7)</f>
         <v>med:BusinessRule_10</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -37582,7 +37606,7 @@
     </row>
     <row r="18" ht="165.75">
       <c r="A18" s="2" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>med:BusinessRule_11</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -37603,7 +37627,7 @@
     </row>
     <row r="19" ht="114.75">
       <c r="A19" s="2" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>med:BusinessRule_12</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -37624,7 +37648,7 @@
     </row>
     <row r="20" ht="127.5">
       <c r="A20" s="2" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>med:BusinessRule_13</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -37645,7 +37669,7 @@
     </row>
     <row r="21" ht="140.25">
       <c r="A21" s="2" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>med:BusinessRule_14</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -37660,13 +37684,13 @@
       <c r="E21" s="8" t="s">
         <v>771</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="91" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="22" ht="140.25">
       <c r="A22" s="2" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>med:BusinessRule_15</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -37681,13 +37705,13 @@
       <c r="E22" s="8" t="s">
         <v>774</v>
       </c>
-      <c r="F22" s="91" t="s">
+      <c r="F22" s="97" t="s">
         <v>775</v>
       </c>
     </row>
     <row r="23" ht="153">
       <c r="A23" s="2" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>med:BusinessRule_16</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -37707,7 +37731,7 @@
       </c>
     </row>
     <row r="24" ht="25.5">
-      <c r="D24" s="92" t="s">
+      <c r="D24" s="98" t="s">
         <v>779</v>
       </c>
       <c r="E24" s="8"/>
@@ -40663,7 +40687,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75">
-      <c r="A1" s="90" t="str">
+      <c r="A1" s="96" t="str">
         <f>Classes!A1</f>
         <v xml:space="preserve">URI de l'ontologie</v>
       </c>
@@ -40682,11 +40706,11 @@
       <c r="G3" s="8"/>
     </row>
     <row r="4" ht="35.25" customHeight="1">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="99" t="s">
         <v>780</v>
       </c>
-      <c r="B4" s="93"/>
-      <c r="C4" s="93"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
       <c r="G4" s="8"/>
     </row>
     <row r="5" ht="12.75">
@@ -40731,44 +40755,44 @@
         <v>788</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>255</v>
+        <v>789</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="9" ht="127.5">
       <c r="A9" s="2" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>788</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="10" ht="12.75">
@@ -40779,7 +40803,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="94"/>
+      <c r="H10" s="100"/>
     </row>
     <row r="11" ht="12.75">
       <c r="F11" s="8"/>
@@ -43789,7 +43813,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75">
-      <c r="A1" s="90" t="str">
+      <c r="A1" s="96" t="str">
         <f>Classes!A1</f>
         <v xml:space="preserve">URI de l'ontologie</v>
       </c>
@@ -43808,11 +43832,11 @@
       <c r="D3" s="8"/>
     </row>
     <row r="4" ht="29.25" customHeight="1">
-      <c r="A4" s="93" t="s">
-        <v>798</v>
-      </c>
-      <c r="B4" s="93"/>
-      <c r="C4" s="93"/>
+      <c r="A4" s="99" t="s">
+        <v>799</v>
+      </c>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
       <c r="D4" s="8"/>
     </row>
     <row r="5" ht="12.75">
@@ -43831,34 +43855,34 @@
         <v>15</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
@@ -43877,69 +43901,69 @@
     </row>
     <row r="8" ht="127.5">
       <c r="A8" s="8" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E8" s="2" t="str">
-        <f t="shared" ref="E8:E9" si="23">CONCATENATE(A8,"-nodeValidator")</f>
+        <f t="shared" ref="E8:E9" si="24">CONCATENATE(A8,"-nodeValidator")</f>
         <v>med:Component_sousClasseDe-nodeValidator</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="I8" s="2" t="str">
         <f>CONCATENATE(A8,"-propertyValidator")</f>
         <v>med:Component_sousClasseDe-propertyValidator</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="9" ht="191.25">
       <c r="A9" s="8" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E9" s="2" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>med:Component_closedBySuperClasses-nodeValidator</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="10" ht="12.75">
@@ -47924,58 +47948,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="96" t="str">
+      <c r="B1" s="102" t="str">
         <f>Classes!B1</f>
         <v>http://data.esante.gouv.fr/ansm/medicament</v>
       </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
     </row>
     <row r="2">
-      <c r="A2" s="97"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
+      <c r="A2" s="103"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
     </row>
     <row r="3">
-      <c r="A3" s="97"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
+      <c r="A3" s="103"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
     </row>
     <row r="4">
-      <c r="A4" s="97"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="97"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
     </row>
     <row r="5">
-      <c r="A5" s="97"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
+      <c r="A5" s="103"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
     </row>
     <row r="6">
-      <c r="A6" s="97"/>
-      <c r="B6" s="97"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
+      <c r="A6" s="103"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
     </row>
     <row r="7">
-      <c r="A7" s="98" t="s">
+      <c r="A7" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="98" t="s">
+      <c r="B7" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="98" t="s">
-        <v>822</v>
-      </c>
-      <c r="D7" s="98" t="s">
+      <c r="C7" s="104" t="s">
         <v>823</v>
+      </c>
+      <c r="D7" s="104" t="s">
+        <v>824</v>
       </c>
     </row>
     <row r="8" ht="56.25" customHeight="1">
@@ -47983,10 +48007,10 @@
         <v>56</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C8" s="20"/>
-      <c r="D8" s="99">
+      <c r="D8" s="105">
         <v>1</v>
       </c>
     </row>
@@ -47995,7 +48019,7 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -48005,11 +48029,11 @@
       <c r="A10" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="100" t="s">
-        <v>826</v>
-      </c>
-      <c r="C10" s="97"/>
-      <c r="D10" s="99">
+      <c r="B10" s="106" t="s">
+        <v>827</v>
+      </c>
+      <c r="C10" s="103"/>
+      <c r="D10" s="105">
         <v>3</v>
       </c>
     </row>
@@ -48018,10 +48042,10 @@
         <v>171</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="99">
+      <c r="D11" s="105">
         <v>4</v>
       </c>
     </row>
